--- a/data/BESTE (TRY).xlsx
+++ b/data/BESTE (TRY).xlsx
@@ -403,1028 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F108"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
-    <col min="2" max="2" customWidth="1" width="20"/>
-    <col min="3" max="3" customWidth="1" width="20"/>
-    <col min="4" max="4" customWidth="1" width="20"/>
-    <col min="5" max="5" customWidth="1" width="20"/>
-    <col min="6" max="6" customWidth="1" width="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Kalem</v>
-      </c>
-      <c r="B1" t="str">
-        <v>2025/12</v>
-      </c>
-      <c r="C1" t="str">
-        <v>2025/9</v>
-      </c>
-      <c r="D1" t="str">
-        <v>2024/12</v>
-      </c>
-      <c r="E1" t="str">
-        <v>2023/12</v>
-      </c>
-      <c r="F1" t="str">
-        <v>2022/12</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Dönen Varlıklar</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B3">
-        <v>68795052</v>
-      </c>
-      <c r="C3">
-        <v>8638520</v>
-      </c>
-      <c r="D3">
-        <v>11262460</v>
-      </c>
-      <c r="E3">
-        <v>22318833</v>
-      </c>
-      <c r="F3">
-        <v>10051791</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlar</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">    Ticari Alacaklar</v>
-      </c>
-      <c r="B7">
-        <v>51594687</v>
-      </c>
-      <c r="C7">
-        <v>82188321</v>
-      </c>
-      <c r="D7">
-        <v>33806359</v>
-      </c>
-      <c r="E7">
-        <v>37220175</v>
-      </c>
-      <c r="F7">
-        <v>24357849</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">    Diğer Alacaklar</v>
-      </c>
-      <c r="B10">
-        <v>708640</v>
-      </c>
-      <c r="D10">
-        <v>1207997</v>
-      </c>
-      <c r="E10">
-        <v>239795</v>
-      </c>
-      <c r="F10">
-        <v>5224402</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">    Stoklar</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v xml:space="preserve">    Proje Halindeki Stoklar</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>853878</v>
-      </c>
-      <c r="D17">
-        <v>223324</v>
-      </c>
-      <c r="E17">
-        <v>99647</v>
-      </c>
-      <c r="F17">
-        <v>368675</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
-      </c>
-      <c r="B21">
-        <v>543629</v>
-      </c>
-      <c r="C21">
-        <v>486916</v>
-      </c>
-      <c r="D21">
-        <v>243681</v>
-      </c>
-      <c r="E21">
-        <v>1889275</v>
-      </c>
-      <c r="F21">
-        <v>1802218</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
-      </c>
-      <c r="B24">
-        <v>121642008</v>
-      </c>
-      <c r="C24">
-        <v>92167635</v>
-      </c>
-      <c r="D24">
-        <v>46743821</v>
-      </c>
-      <c r="E24">
-        <v>61767725</v>
-      </c>
-      <c r="F24">
-        <v>41804935</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlar</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v xml:space="preserve">    Ticari Alacaklar</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v xml:space="preserve">    Diğer Alacaklar</v>
-      </c>
-      <c r="B30">
-        <v>324117</v>
-      </c>
-      <c r="C30">
-        <v>403114</v>
-      </c>
-      <c r="D30">
-        <v>383426</v>
-      </c>
-      <c r="E30">
-        <v>312873</v>
-      </c>
-      <c r="F30">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">    Stoklar</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
-      </c>
-      <c r="F37">
-        <v>50405973</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v xml:space="preserve">    Maddi Duran Varlıklar</v>
-      </c>
-      <c r="B39">
-        <v>4663238585</v>
-      </c>
-      <c r="C39">
-        <v>4536412943</v>
-      </c>
-      <c r="D39">
-        <v>3925991360</v>
-      </c>
-      <c r="E39">
-        <v>2738078086</v>
-      </c>
-      <c r="F39">
-        <v>1785693132</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
-      </c>
-      <c r="B40">
-        <v>6114681</v>
-      </c>
-      <c r="C40">
-        <v>6483196</v>
-      </c>
-      <c r="D40">
-        <v>7865919</v>
-      </c>
-      <c r="E40">
-        <v>3208450</v>
-      </c>
-      <c r="F40">
-        <v>1163983</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
-      </c>
-      <c r="B41">
-        <v>3562306</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
-      </c>
-      <c r="B42">
-        <v>1920600</v>
-      </c>
-      <c r="C42">
-        <v>1330705</v>
-      </c>
-      <c r="D42">
-        <v>1548019</v>
-      </c>
-      <c r="E42">
-        <v>1844837</v>
-      </c>
-      <c r="F42">
-        <v>1183988</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v xml:space="preserve">    Diğer Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v xml:space="preserve">    Toplam Duran Varlıklar</v>
-      </c>
-      <c r="B47">
-        <v>4675160289</v>
-      </c>
-      <c r="C47">
-        <v>4544629958</v>
-      </c>
-      <c r="D47">
-        <v>3935788734</v>
-      </c>
-      <c r="E47">
-        <v>2743444246</v>
-      </c>
-      <c r="F47">
-        <v>1838449052</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v xml:space="preserve">    Toplam Varlıklar</v>
-      </c>
-      <c r="B48">
-        <v>4796802297</v>
-      </c>
-      <c r="C48">
-        <v>4636797593</v>
-      </c>
-      <c r="D48">
-        <v>3982532555</v>
-      </c>
-      <c r="E48">
-        <v>2805211971</v>
-      </c>
-      <c r="F48">
-        <v>1880253987</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Kısa Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v xml:space="preserve">    Finansal Borçlar</v>
-      </c>
-      <c r="B50">
-        <v>221207880</v>
-      </c>
-      <c r="C50">
-        <v>152649712</v>
-      </c>
-      <c r="D50">
-        <v>166810514</v>
-      </c>
-      <c r="E50">
-        <v>213162125</v>
-      </c>
-      <c r="F50">
-        <v>144362439</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">    Ticari Borçlar</v>
-      </c>
-      <c r="B52">
-        <v>17894916</v>
-      </c>
-      <c r="C52">
-        <v>33656896</v>
-      </c>
-      <c r="D52">
-        <v>14370019</v>
-      </c>
-      <c r="E52">
-        <v>4009125</v>
-      </c>
-      <c r="F52">
-        <v>1830785</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
-      </c>
-      <c r="B54">
-        <v>624136</v>
-      </c>
-      <c r="C54">
-        <v>1610122</v>
-      </c>
-      <c r="D54">
-        <v>378205</v>
-      </c>
-      <c r="E54">
-        <v>1036413</v>
-      </c>
-      <c r="F54">
-        <v>330515</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v xml:space="preserve">    Diğer Borçlar</v>
-      </c>
-      <c r="B55">
-        <v>25034790</v>
-      </c>
-      <c r="C55">
-        <v>41375272</v>
-      </c>
-      <c r="D55">
-        <v>45078523</v>
-      </c>
-      <c r="E55">
-        <v>45576883</v>
-      </c>
-      <c r="F55">
-        <v>42137918</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
-      </c>
-      <c r="F60">
-        <v>184625</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
-      </c>
-      <c r="B62">
-        <v>741021</v>
-      </c>
-      <c r="C62">
-        <v>1320923</v>
-      </c>
-      <c r="D62">
-        <v>1031384</v>
-      </c>
-      <c r="E62">
-        <v>1041514</v>
-      </c>
-      <c r="F62">
-        <v>550085</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B66">
-        <v>265502743</v>
-      </c>
-      <c r="C66">
-        <v>230612925</v>
-      </c>
-      <c r="D66">
-        <v>227668645</v>
-      </c>
-      <c r="E66">
-        <v>264826060</v>
-      </c>
-      <c r="F66">
-        <v>189396367</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Uzun Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v xml:space="preserve">    Finansal Borçlar</v>
-      </c>
-      <c r="B68">
-        <v>117913883</v>
-      </c>
-      <c r="C68">
-        <v>139709436</v>
-      </c>
-      <c r="D68">
-        <v>200005538</v>
-      </c>
-      <c r="E68">
-        <v>263401307</v>
-      </c>
-      <c r="F68">
-        <v>297187769</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v xml:space="preserve">    Ticari Borçlar</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v xml:space="preserve">    Diğer Borçlar</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
-      </c>
-      <c r="B80">
-        <v>2348569</v>
-      </c>
-      <c r="C80">
-        <v>2698854</v>
-      </c>
-      <c r="D80">
-        <v>855688</v>
-      </c>
-      <c r="E80">
-        <v>420419</v>
-      </c>
-      <c r="F80">
-        <v>242882</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
-      </c>
-      <c r="B82">
-        <v>770576622</v>
-      </c>
-      <c r="C82">
-        <v>707770061</v>
-      </c>
-      <c r="D82">
-        <v>582511798</v>
-      </c>
-      <c r="E82">
-        <v>351135952</v>
-      </c>
-      <c r="F82">
-        <v>235040755</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B84">
-        <v>890839074</v>
-      </c>
-      <c r="C84">
-        <v>850178351</v>
-      </c>
-      <c r="D84">
-        <v>783373024</v>
-      </c>
-      <c r="E84">
-        <v>614957678</v>
-      </c>
-      <c r="F84">
-        <v>532471406</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Özkaynaklar</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
-      </c>
-      <c r="B86">
-        <v>3640460480</v>
-      </c>
-      <c r="C86">
-        <v>3556006317</v>
-      </c>
-      <c r="D86">
-        <v>2971490886</v>
-      </c>
-      <c r="E86">
-        <v>1925428233</v>
-      </c>
-      <c r="F86">
-        <v>1159866961</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v xml:space="preserve">    Ödenmiş Sermaye</v>
-      </c>
-      <c r="B87">
-        <v>150000000</v>
-      </c>
-      <c r="C87">
-        <v>150000000</v>
-      </c>
-      <c r="D87">
-        <v>150000000</v>
-      </c>
-      <c r="E87">
-        <v>61475000</v>
-      </c>
-      <c r="F87">
-        <v>50000000</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v xml:space="preserve">    Sermaye Avansı</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi Teşebbüs veya İşletmeleri İçeren Birleşmelerin Etkisi</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
-      </c>
-      <c r="B97">
-        <v>665226146</v>
-      </c>
-      <c r="C97">
-        <v>665468811</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
-      </c>
-      <c r="B98">
-        <v>2053903308</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v xml:space="preserve">    Diğer Özkaynak Payları</v>
-      </c>
-      <c r="C100">
-        <v>1980629349</v>
-      </c>
-      <c r="D100">
-        <v>2240417556</v>
-      </c>
-      <c r="E100">
-        <v>1316356992</v>
-      </c>
-      <c r="F100">
-        <v>596363502</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v xml:space="preserve">    Diğer Yedekler</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
-      </c>
-      <c r="B103">
-        <v>581073330</v>
-      </c>
-      <c r="C103">
-        <v>581073330</v>
-      </c>
-      <c r="D103">
-        <v>459071241</v>
-      </c>
-      <c r="E103">
-        <v>494686489</v>
-      </c>
-      <c r="F103">
-        <v>443806782</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
-      </c>
-      <c r="B104">
-        <v>190257696</v>
-      </c>
-      <c r="C104">
-        <v>178834827</v>
-      </c>
-      <c r="D104">
-        <v>122002089</v>
-      </c>
-      <c r="E104">
-        <v>52909752</v>
-      </c>
-      <c r="F104">
-        <v>69696677</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v xml:space="preserve">    Azınlık Payları</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v xml:space="preserve">    Toplam Özkaynaklar</v>
-      </c>
-      <c r="B106">
-        <v>3640460480</v>
-      </c>
-      <c r="C106">
-        <v>3556006317</v>
-      </c>
-      <c r="D106">
-        <v>2971490886</v>
-      </c>
-      <c r="E106">
-        <v>1925428233</v>
-      </c>
-      <c r="F106">
-        <v>1158386214</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v xml:space="preserve">    Toplam Kaynaklar</v>
-      </c>
-      <c r="B107">
-        <v>4796802297</v>
-      </c>
-      <c r="C107">
-        <v>4636797593</v>
-      </c>
-      <c r="D107">
-        <v>3982532555</v>
-      </c>
-      <c r="E107">
-        <v>2805211971</v>
-      </c>
-      <c r="F107">
-        <v>1880253987</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1440,16 +419,16 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
-      </c>
-      <c r="E1" t="str">
-        <v>2024/9</v>
       </c>
       <c r="F1" t="str">
         <v>2023/12</v>
@@ -1460,568 +439,1095 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Dönen Varlıklar</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">    Satış Gelirleri</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>448686813</v>
+        <v>46706240</v>
       </c>
       <c r="C3">
-        <v>346581538</v>
+        <v>68795052</v>
       </c>
       <c r="D3">
-        <v>345482207</v>
+        <v>8638520</v>
       </c>
       <c r="E3">
-        <v>265504087</v>
+        <v>11262460</v>
       </c>
       <c r="F3">
-        <v>287515179</v>
+        <v>22318833</v>
       </c>
       <c r="G3">
-        <v>178947454</v>
+        <v>10051791</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">    Toplam Hasılat</v>
+        <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">    Yurt İçi Satışlar</v>
+        <v xml:space="preserve">    Finansal Yatırımlar</v>
+      </c>
+      <c r="B5">
+        <v>533378718</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">    Yurt Dışı Satışlar</v>
+        <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">    Satışların Maliyeti (-)</v>
+        <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>-323651484</v>
+        <v>39167605</v>
       </c>
       <c r="C7">
-        <v>-246495873</v>
+        <v>51594687</v>
       </c>
       <c r="D7">
-        <v>-257480356</v>
+        <v>82188321</v>
       </c>
       <c r="E7">
-        <v>-149830831</v>
+        <v>33806359</v>
       </c>
       <c r="F7">
-        <v>-188330683</v>
+        <v>37220175</v>
       </c>
       <c r="G7">
-        <v>-81596607</v>
+        <v>24357849</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
-      </c>
-      <c r="B8">
-        <v>125035329</v>
-      </c>
-      <c r="C8">
-        <v>100085665</v>
-      </c>
-      <c r="D8">
-        <v>88001851</v>
-      </c>
-      <c r="E8">
-        <v>115673256</v>
-      </c>
-      <c r="F8">
-        <v>99184496</v>
-      </c>
-      <c r="G8">
-        <v>97350847</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
+        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
+        <v xml:space="preserve">    Diğer Alacaklar</v>
+      </c>
+      <c r="B10">
+        <v>708445</v>
+      </c>
+      <c r="C10">
+        <v>708640</v>
+      </c>
+      <c r="E10">
+        <v>1207997</v>
+      </c>
+      <c r="F10">
+        <v>239795</v>
+      </c>
+      <c r="G10">
+        <v>5224402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar Gerçeğe Uygun Değer Farkları</v>
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    Brüt Kar (Zarar)</v>
-      </c>
-      <c r="B13">
-        <v>125035329</v>
-      </c>
-      <c r="C13">
-        <v>100085665</v>
-      </c>
-      <c r="D13">
-        <v>88001851</v>
-      </c>
-      <c r="E13">
-        <v>115673256</v>
-      </c>
-      <c r="F13">
-        <v>99184496</v>
-      </c>
-      <c r="G13">
-        <v>97350847</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">    Stoklar</v>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
-      </c>
-      <c r="B15">
-        <v>-18658866</v>
-      </c>
-      <c r="C15">
-        <v>-12695234</v>
-      </c>
-      <c r="D15">
-        <v>-25065759</v>
-      </c>
-      <c r="E15">
-        <v>-6792315</v>
-      </c>
-      <c r="F15">
-        <v>-15872106</v>
-      </c>
-      <c r="G15">
-        <v>-10691285</v>
+        <v xml:space="preserve">    Proje Halindeki Stoklar</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
+        <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
+        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
+      </c>
+      <c r="B17">
+        <v>1993432</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>853878</v>
+      </c>
+      <c r="E17">
+        <v>223324</v>
+      </c>
+      <c r="F17">
+        <v>99647</v>
+      </c>
+      <c r="G17">
+        <v>368675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
-      </c>
-      <c r="B18">
-        <v>2679624</v>
-      </c>
-      <c r="C18">
-        <v>2764396</v>
-      </c>
-      <c r="D18">
-        <v>2622648</v>
-      </c>
-      <c r="E18">
-        <v>4344339</v>
-      </c>
-      <c r="F18">
-        <v>6058934</v>
-      </c>
-      <c r="G18">
-        <v>10801617</v>
+        <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
-      </c>
-      <c r="B19">
-        <v>-15373582</v>
-      </c>
-      <c r="C19">
-        <v>-17020945</v>
-      </c>
-      <c r="D19">
-        <v>-2840412</v>
-      </c>
-      <c r="E19">
-        <v>-8985861</v>
-      </c>
-      <c r="F19">
-        <v>-878099</v>
-      </c>
-      <c r="G19">
-        <v>-4621841</v>
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    Diğer Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+        <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>93682505</v>
+        <v>552116</v>
       </c>
       <c r="C21">
-        <v>73133882</v>
+        <v>543629</v>
       </c>
       <c r="D21">
-        <v>62718328</v>
+        <v>486916</v>
       </c>
       <c r="E21">
-        <v>104239419</v>
+        <v>243681</v>
       </c>
       <c r="F21">
-        <v>88493225</v>
+        <v>1889275</v>
       </c>
       <c r="G21">
-        <v>92839338</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>1802218</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    Ödenecek Kar Paylarının Defter Değeri ile Dağıtılan Nakit Dışı Varlıkların Değeri Arasındaki Fark</v>
+        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Finansal Tablo Dışı Bırakılmasından Kaynaklanan Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
+      </c>
+      <c r="B24">
+        <v>622506556</v>
+      </c>
+      <c r="C24">
+        <v>121642008</v>
+      </c>
+      <c r="D24">
+        <v>92167635</v>
+      </c>
+      <c r="E24">
+        <v>46743821</v>
+      </c>
+      <c r="F24">
+        <v>61767725</v>
+      </c>
+      <c r="G24">
+        <v>41804935</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
-      </c>
-      <c r="F25">
-        <v>1281157</v>
-      </c>
-      <c r="G25">
-        <v>6272173</v>
+        <v>Duran Varlıklar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
-      </c>
-      <c r="F26">
-        <v>-19680306</v>
+        <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
+        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
+        <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">    İştirakler, Müşterek Kontrol Edilen İşletmeler ve Bağlı Ortaklıklardan Diğer Gelirler (Giderler)</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Diğer Alacaklar</v>
+      </c>
+      <c r="B30">
+        <v>357891</v>
+      </c>
+      <c r="C30">
+        <v>324117</v>
+      </c>
+      <c r="D30">
+        <v>403114</v>
+      </c>
+      <c r="E30">
+        <v>383426</v>
+      </c>
+      <c r="F30">
+        <v>312873</v>
+      </c>
+      <c r="G30">
+        <v>1976</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
-      </c>
-      <c r="B33">
-        <v>93682505</v>
-      </c>
-      <c r="C33">
-        <v>73133882</v>
-      </c>
-      <c r="D33">
-        <v>62718328</v>
-      </c>
-      <c r="E33">
-        <v>104239419</v>
-      </c>
-      <c r="F33">
-        <v>70094076</v>
-      </c>
-      <c r="G33">
-        <v>99111511</v>
-      </c>
-    </row>
-    <row r="34"/>
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">    Stoklar</v>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
-      </c>
-      <c r="B35">
-        <v>226241670</v>
-      </c>
-      <c r="C35">
-        <v>163265404</v>
-      </c>
-      <c r="D35">
-        <v>129246505</v>
-      </c>
-      <c r="E35">
-        <v>39608134</v>
-      </c>
-      <c r="F35">
-        <v>213370889</v>
-      </c>
-      <c r="G35">
-        <v>161654973</v>
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
-      </c>
-      <c r="B36">
-        <v>-72684977</v>
-      </c>
-      <c r="C36">
-        <v>-37857848</v>
-      </c>
-      <c r="D36">
-        <v>-87348593</v>
-      </c>
-      <c r="E36">
-        <v>-61998142</v>
-      </c>
-      <c r="F36">
-        <v>-245531920</v>
-      </c>
-      <c r="G36">
-        <v>-191427919</v>
+        <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
+      </c>
+      <c r="G37">
+        <v>50405973</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
-      </c>
-      <c r="B38">
-        <v>247239198</v>
-      </c>
-      <c r="C38">
-        <v>198541438</v>
-      </c>
-      <c r="D38">
-        <v>104616240</v>
-      </c>
-      <c r="E38">
-        <v>81849411</v>
-      </c>
-      <c r="F38">
-        <v>37933045</v>
-      </c>
-      <c r="G38">
-        <v>69338565</v>
-      </c>
-    </row>
-    <row r="39"/>
+        <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    Maddi Duran Varlıklar</v>
+      </c>
+      <c r="B39">
+        <v>4790833692</v>
+      </c>
+      <c r="C39">
+        <v>4663238585</v>
+      </c>
+      <c r="D39">
+        <v>4536412943</v>
+      </c>
+      <c r="E39">
+        <v>3925991360</v>
+      </c>
+      <c r="F39">
+        <v>2738078086</v>
+      </c>
+      <c r="G39">
+        <v>1785693132</v>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
+        <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>-56981502</v>
+        <v>9815489</v>
+      </c>
+      <c r="C40">
+        <v>6114681</v>
       </c>
       <c r="D40">
-        <v>17385849</v>
+        <v>6483196</v>
+      </c>
+      <c r="E40">
+        <v>7865919</v>
       </c>
       <c r="F40">
-        <v>14976707</v>
+        <v>3208450</v>
       </c>
       <c r="G40">
-        <v>358113</v>
+        <v>1163983</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
-      </c>
-      <c r="G41">
-        <v>-33</v>
+        <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
+      </c>
+      <c r="B41">
+        <v>3445347</v>
+      </c>
+      <c r="C41">
+        <v>3562306</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
+        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>-56981502</v>
+        <v>5524</v>
       </c>
       <c r="C42">
-        <v>-19706611</v>
+        <v>1920600</v>
       </c>
       <c r="D42">
-        <v>17385849</v>
+        <v>1330705</v>
       </c>
       <c r="E42">
-        <v>-1082270</v>
+        <v>1548019</v>
       </c>
       <c r="F42">
-        <v>14976707</v>
+        <v>1844837</v>
       </c>
       <c r="G42">
-        <v>358080</v>
+        <v>1183988</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-      <c r="B43">
-        <v>190257696</v>
-      </c>
-      <c r="C43">
-        <v>198541438</v>
-      </c>
-      <c r="D43">
-        <v>122002089</v>
-      </c>
-      <c r="E43">
-        <v>81849411</v>
-      </c>
-      <c r="F43">
-        <v>52909752</v>
-      </c>
-      <c r="G43">
-        <v>69696678</v>
+        <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-    </row>
-    <row r="45"/>
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Duran Varlıklar</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
-      </c>
-      <c r="B46">
-        <v>190257696</v>
-      </c>
-      <c r="C46">
-        <v>178834827</v>
-      </c>
-      <c r="D46">
-        <v>122002089</v>
-      </c>
-      <c r="E46">
-        <v>80767141</v>
-      </c>
-      <c r="F46">
-        <v>52909752</v>
-      </c>
-      <c r="G46">
-        <v>69696678</v>
+        <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    Azınlık Payları</v>
+        <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>4804457943</v>
+      </c>
+      <c r="C47">
+        <v>4675160289</v>
+      </c>
+      <c r="D47">
+        <v>4544629958</v>
+      </c>
+      <c r="E47">
+        <v>3935788734</v>
+      </c>
+      <c r="F47">
+        <v>2743444246</v>
+      </c>
+      <c r="G47">
+        <v>1838449052</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    Ana Ortaklık Payları</v>
+        <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>190257696</v>
+        <v>5426964499</v>
       </c>
       <c r="C48">
-        <v>178834827</v>
+        <v>4796802297</v>
       </c>
       <c r="D48">
-        <v>122002089</v>
+        <v>4636797593</v>
       </c>
       <c r="E48">
-        <v>80767141</v>
+        <v>3982532555</v>
       </c>
       <c r="F48">
-        <v>52909752</v>
+        <v>2805211971</v>
       </c>
       <c r="G48">
-        <v>69696678</v>
-      </c>
-    </row>
-    <row r="49"/>
+        <v>1880253987</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Kısa Vadeli Yükümlülükler</v>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    Amortisman</v>
+        <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>155543420</v>
+        <v>181274705</v>
       </c>
       <c r="C50">
-        <v>111727030</v>
+        <v>221207880</v>
       </c>
       <c r="D50">
-        <v>237253862</v>
+        <v>152649712</v>
       </c>
       <c r="E50">
-        <v>79585953</v>
+        <v>166810514</v>
       </c>
       <c r="F50">
-        <v>84819402</v>
+        <v>213162125</v>
       </c>
       <c r="G50">
-        <v>55472384</v>
+        <v>144362439</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Ticari Borçlar</v>
+      </c>
+      <c r="B52">
+        <v>17777251</v>
+      </c>
+      <c r="C52">
+        <v>17894916</v>
+      </c>
+      <c r="D52">
+        <v>33656896</v>
+      </c>
+      <c r="E52">
+        <v>14370019</v>
+      </c>
+      <c r="F52">
+        <v>4009125</v>
+      </c>
+      <c r="G52">
+        <v>1830785</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
+      </c>
+      <c r="B54">
+        <v>2548393</v>
+      </c>
+      <c r="C54">
+        <v>624136</v>
+      </c>
+      <c r="D54">
+        <v>1610122</v>
+      </c>
+      <c r="E54">
+        <v>378205</v>
+      </c>
+      <c r="F54">
+        <v>1036413</v>
+      </c>
+      <c r="G54">
+        <v>330515</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">    Diğer Borçlar</v>
+      </c>
+      <c r="B55">
+        <v>19246970</v>
+      </c>
+      <c r="C55">
+        <v>25034790</v>
+      </c>
+      <c r="D55">
+        <v>41375272</v>
+      </c>
+      <c r="E55">
+        <v>45078523</v>
+      </c>
+      <c r="F55">
+        <v>45576883</v>
+      </c>
+      <c r="G55">
+        <v>42137918</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
+      </c>
+      <c r="G60">
+        <v>184625</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
+      </c>
+      <c r="B62">
+        <v>828928</v>
+      </c>
+      <c r="C62">
+        <v>741021</v>
+      </c>
+      <c r="D62">
+        <v>1320923</v>
+      </c>
+      <c r="E62">
+        <v>1031384</v>
+      </c>
+      <c r="F62">
+        <v>1041514</v>
+      </c>
+      <c r="G62">
+        <v>550085</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B66">
+        <v>221676247</v>
+      </c>
+      <c r="C66">
+        <v>265502743</v>
+      </c>
+      <c r="D66">
+        <v>230612925</v>
+      </c>
+      <c r="E66">
+        <v>227668645</v>
+      </c>
+      <c r="F66">
+        <v>264826060</v>
+      </c>
+      <c r="G66">
+        <v>189396367</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Uzun Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">    Finansal Borçlar</v>
+      </c>
+      <c r="B68">
+        <v>105220983</v>
+      </c>
+      <c r="C68">
+        <v>117913883</v>
+      </c>
+      <c r="D68">
+        <v>139709436</v>
+      </c>
+      <c r="E68">
+        <v>200005538</v>
+      </c>
+      <c r="F68">
+        <v>263401307</v>
+      </c>
+      <c r="G68">
+        <v>297187769</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Ticari Borçlar</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">    Diğer Borçlar</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
+      </c>
+      <c r="B80">
+        <v>1741373</v>
+      </c>
+      <c r="C80">
+        <v>2348569</v>
+      </c>
+      <c r="D80">
+        <v>2698854</v>
+      </c>
+      <c r="E80">
+        <v>855688</v>
+      </c>
+      <c r="F80">
+        <v>420419</v>
+      </c>
+      <c r="G80">
+        <v>242882</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
+      </c>
+      <c r="B82">
+        <v>760695156</v>
+      </c>
+      <c r="C82">
+        <v>770576622</v>
+      </c>
+      <c r="D82">
+        <v>707770061</v>
+      </c>
+      <c r="E82">
+        <v>582511798</v>
+      </c>
+      <c r="F82">
+        <v>351135952</v>
+      </c>
+      <c r="G82">
+        <v>235040755</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B84">
+        <v>867657512</v>
+      </c>
+      <c r="C84">
+        <v>890839074</v>
+      </c>
+      <c r="D84">
+        <v>850178351</v>
+      </c>
+      <c r="E84">
+        <v>783373024</v>
+      </c>
+      <c r="F84">
+        <v>614957678</v>
+      </c>
+      <c r="G84">
+        <v>532471406</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Özkaynaklar</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
+      </c>
+      <c r="B86">
+        <v>4337630740</v>
+      </c>
+      <c r="C86">
+        <v>3640460480</v>
+      </c>
+      <c r="D86">
+        <v>3556006317</v>
+      </c>
+      <c r="E86">
+        <v>2971490886</v>
+      </c>
+      <c r="F86">
+        <v>1925428233</v>
+      </c>
+      <c r="G86">
+        <v>1159866961</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">    Ödenmiş Sermaye</v>
+      </c>
+      <c r="B87">
+        <v>188205000</v>
+      </c>
+      <c r="C87">
+        <v>150000000</v>
+      </c>
+      <c r="D87">
+        <v>150000000</v>
+      </c>
+      <c r="E87">
+        <v>150000000</v>
+      </c>
+      <c r="F87">
+        <v>61475000</v>
+      </c>
+      <c r="G87">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">    Sermaye Avansı</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
+      </c>
+      <c r="B94">
+        <v>506242675</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">    Ortak Kontrole Tabi Teşebbüs veya İşletmeleri İçeren Birleşmelerin Etkisi</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
+      </c>
+      <c r="B97">
+        <v>666774209</v>
+      </c>
+      <c r="C97">
+        <v>665226146</v>
+      </c>
+      <c r="D97">
+        <v>665468811</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
+      </c>
+      <c r="B98">
+        <v>2245908680</v>
+      </c>
+      <c r="C98">
+        <v>2053903308</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve">    Diğer Özkaynak Payları</v>
+      </c>
+      <c r="D100">
+        <v>1980629349</v>
+      </c>
+      <c r="E100">
+        <v>2240417556</v>
+      </c>
+      <c r="F100">
+        <v>1316356992</v>
+      </c>
+      <c r="G100">
+        <v>596363502</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Diğer Yedekler</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
+      </c>
+      <c r="B103">
+        <v>771331026</v>
+      </c>
+      <c r="C103">
+        <v>581073330</v>
+      </c>
+      <c r="D103">
+        <v>581073330</v>
+      </c>
+      <c r="E103">
+        <v>459071241</v>
+      </c>
+      <c r="F103">
+        <v>494686489</v>
+      </c>
+      <c r="G103">
+        <v>443806782</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
+      </c>
+      <c r="B104">
+        <v>-40830850</v>
+      </c>
+      <c r="C104">
+        <v>190257696</v>
+      </c>
+      <c r="D104">
+        <v>178834827</v>
+      </c>
+      <c r="E104">
+        <v>122002089</v>
+      </c>
+      <c r="F104">
+        <v>52909752</v>
+      </c>
+      <c r="G104">
+        <v>69696677</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    Azınlık Payları</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    Toplam Özkaynaklar</v>
+      </c>
+      <c r="B106">
+        <v>4337630740</v>
+      </c>
+      <c r="C106">
+        <v>3640460480</v>
+      </c>
+      <c r="D106">
+        <v>3556006317</v>
+      </c>
+      <c r="E106">
+        <v>2971490886</v>
+      </c>
+      <c r="F106">
+        <v>1925428233</v>
+      </c>
+      <c r="G106">
+        <v>1158386214</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">    Toplam Kaynaklar</v>
+      </c>
+      <c r="B107">
+        <v>5426964499</v>
+      </c>
+      <c r="C107">
+        <v>4796802297</v>
+      </c>
+      <c r="D107">
+        <v>4636797593</v>
+      </c>
+      <c r="E107">
+        <v>3982532555</v>
+      </c>
+      <c r="F107">
+        <v>2805211971</v>
+      </c>
+      <c r="G107">
+        <v>1880253987</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2030,6 +1536,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2037,21 +1545,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2065,10 +1579,28 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>102105275</v>
+        <v>51818936</v>
+      </c>
+      <c r="C3">
+        <v>448686813</v>
       </c>
       <c r="D3">
-        <v>79978120</v>
+        <v>346581538</v>
+      </c>
+      <c r="E3">
+        <v>67266312</v>
+      </c>
+      <c r="F3">
+        <v>345482207</v>
+      </c>
+      <c r="G3">
+        <v>265504087</v>
+      </c>
+      <c r="H3">
+        <v>287515179</v>
+      </c>
+      <c r="I3">
+        <v>178947454</v>
       </c>
     </row>
     <row r="4">
@@ -2091,10 +1623,28 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-77155611</v>
+        <v>-76560889</v>
+      </c>
+      <c r="C7">
+        <v>-323651484</v>
       </c>
       <c r="D7">
-        <v>-107649525</v>
+        <v>-246495873</v>
+      </c>
+      <c r="E7">
+        <v>-59848344</v>
+      </c>
+      <c r="F7">
+        <v>-257480356</v>
+      </c>
+      <c r="G7">
+        <v>-149830831</v>
+      </c>
+      <c r="H7">
+        <v>-188330683</v>
+      </c>
+      <c r="I7">
+        <v>-81596607</v>
       </c>
     </row>
     <row r="8">
@@ -2102,26 +1652,62 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>24949664</v>
+        <v>-24741953</v>
+      </c>
+      <c r="C8">
+        <v>125035329</v>
       </c>
       <c r="D8">
-        <v>-27671405</v>
+        <v>100085665</v>
+      </c>
+      <c r="E8">
+        <v>7417968</v>
+      </c>
+      <c r="F8">
+        <v>88001851</v>
+      </c>
+      <c r="G8">
+        <v>115673256</v>
+      </c>
+      <c r="H8">
+        <v>99184496</v>
+      </c>
+      <c r="I8">
+        <v>97350847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2133,10 +1719,28 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>24949664</v>
+        <v>-24741953</v>
+      </c>
+      <c r="C13">
+        <v>125035329</v>
       </c>
       <c r="D13">
-        <v>-27671405</v>
+        <v>100085665</v>
+      </c>
+      <c r="E13">
+        <v>7417968</v>
+      </c>
+      <c r="F13">
+        <v>88001851</v>
+      </c>
+      <c r="G13">
+        <v>115673256</v>
+      </c>
+      <c r="H13">
+        <v>99184496</v>
+      </c>
+      <c r="I13">
+        <v>97350847</v>
       </c>
     </row>
     <row r="14"/>
@@ -2145,10 +1749,28 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-5963632</v>
+        <v>-23130813</v>
+      </c>
+      <c r="C15">
+        <v>-18658866</v>
       </c>
       <c r="D15">
-        <v>-18273444</v>
+        <v>-12695234</v>
+      </c>
+      <c r="E15">
+        <v>-2770069</v>
+      </c>
+      <c r="F15">
+        <v>-25065759</v>
+      </c>
+      <c r="G15">
+        <v>-6792315</v>
+      </c>
+      <c r="H15">
+        <v>-15872106</v>
+      </c>
+      <c r="I15">
+        <v>-10691285</v>
       </c>
     </row>
     <row r="16">
@@ -2166,10 +1788,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>-84772</v>
+        <v>412034</v>
+      </c>
+      <c r="C18">
+        <v>2679624</v>
       </c>
       <c r="D18">
-        <v>-1721691</v>
+        <v>2764396</v>
+      </c>
+      <c r="E18">
+        <v>17303662</v>
+      </c>
+      <c r="F18">
+        <v>2622648</v>
+      </c>
+      <c r="G18">
+        <v>4344339</v>
+      </c>
+      <c r="H18">
+        <v>6058934</v>
+      </c>
+      <c r="I18">
+        <v>10801617</v>
       </c>
     </row>
     <row r="19">
@@ -2177,10 +1817,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>1647363</v>
+        <v>-3598962</v>
+      </c>
+      <c r="C19">
+        <v>-15373582</v>
       </c>
       <c r="D19">
-        <v>6145449</v>
+        <v>-17020945</v>
+      </c>
+      <c r="E19">
+        <v>-973496</v>
+      </c>
+      <c r="F19">
+        <v>-2840412</v>
+      </c>
+      <c r="G19">
+        <v>-8985861</v>
+      </c>
+      <c r="H19">
+        <v>-878099</v>
+      </c>
+      <c r="I19">
+        <v>-4621841</v>
       </c>
     </row>
     <row r="20">
@@ -2193,10 +1851,28 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>20548623</v>
+        <v>-51059694</v>
+      </c>
+      <c r="C21">
+        <v>93682505</v>
       </c>
       <c r="D21">
-        <v>-41521091</v>
+        <v>73133882</v>
+      </c>
+      <c r="E21">
+        <v>20978065</v>
+      </c>
+      <c r="F21">
+        <v>62718328</v>
+      </c>
+      <c r="G21">
+        <v>104239419</v>
+      </c>
+      <c r="H21">
+        <v>88493225</v>
+      </c>
+      <c r="I21">
+        <v>92839338</v>
       </c>
     </row>
     <row r="22"/>
@@ -2214,11 +1890,23 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>25647509</v>
+      </c>
+      <c r="H25">
+        <v>1281157</v>
+      </c>
+      <c r="I25">
+        <v>6272173</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="H26">
+        <v>-19680306</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2255,10 +1943,28 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>20548623</v>
+        <v>-25412185</v>
+      </c>
+      <c r="C33">
+        <v>93682505</v>
       </c>
       <c r="D33">
-        <v>-41521091</v>
+        <v>73133882</v>
+      </c>
+      <c r="E33">
+        <v>20978065</v>
+      </c>
+      <c r="F33">
+        <v>62718328</v>
+      </c>
+      <c r="G33">
+        <v>104239419</v>
+      </c>
+      <c r="H33">
+        <v>70094076</v>
+      </c>
+      <c r="I33">
+        <v>99111511</v>
       </c>
     </row>
     <row r="34"/>
@@ -2267,10 +1973,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>62976266</v>
+        <v>5612971</v>
+      </c>
+      <c r="C35">
+        <v>226241670</v>
       </c>
       <c r="D35">
-        <v>89638371</v>
+        <v>163265404</v>
+      </c>
+      <c r="E35">
+        <v>54248589</v>
+      </c>
+      <c r="F35">
+        <v>129246505</v>
+      </c>
+      <c r="G35">
+        <v>39608134</v>
+      </c>
+      <c r="H35">
+        <v>213370889</v>
+      </c>
+      <c r="I35">
+        <v>161654973</v>
       </c>
     </row>
     <row r="36">
@@ -2278,26 +2002,65 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-34827129</v>
+        <v>-58577736</v>
+      </c>
+      <c r="C36">
+        <v>-72684977</v>
       </c>
       <c r="D36">
-        <v>-25350451</v>
+        <v>-37857848</v>
+      </c>
+      <c r="E36">
+        <v>-52909462</v>
+      </c>
+      <c r="F36">
+        <v>-87348593</v>
+      </c>
+      <c r="G36">
+        <v>-61998142</v>
+      </c>
+      <c r="H36">
+        <v>-245531920</v>
+      </c>
+      <c r="I36">
+        <v>-191427919</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>30491</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>48697760</v>
+        <v>-78346459</v>
+      </c>
+      <c r="C38">
+        <v>247239198</v>
       </c>
       <c r="D38">
-        <v>22766829</v>
+        <v>198541438</v>
+      </c>
+      <c r="E38">
+        <v>22317192</v>
+      </c>
+      <c r="F38">
+        <v>104616240</v>
+      </c>
+      <c r="G38">
+        <v>81849411</v>
+      </c>
+      <c r="H38">
+        <v>37933045</v>
+      </c>
+      <c r="I38">
+        <v>69338565</v>
       </c>
     </row>
     <row r="39"/>
@@ -2305,21 +2068,60 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>37515609</v>
+      </c>
+      <c r="C40">
+        <v>-56981502</v>
+      </c>
+      <c r="E40">
+        <v>13967843</v>
+      </c>
+      <c r="F40">
+        <v>17385849</v>
+      </c>
+      <c r="H40">
+        <v>14976707</v>
+      </c>
+      <c r="I40">
+        <v>358113</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="I41">
+        <v>-33</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-37274891</v>
+        <v>37515609</v>
+      </c>
+      <c r="C42">
+        <v>-56981502</v>
       </c>
       <c r="D42">
-        <v>18468119</v>
+        <v>-19706611</v>
+      </c>
+      <c r="E42">
+        <v>13967843</v>
+      </c>
+      <c r="F42">
+        <v>17385849</v>
+      </c>
+      <c r="G42">
+        <v>-1082270</v>
+      </c>
+      <c r="H42">
+        <v>14976707</v>
+      </c>
+      <c r="I42">
+        <v>358080</v>
       </c>
     </row>
     <row r="43">
@@ -2327,10 +2129,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-8283742</v>
+        <v>-40830850</v>
+      </c>
+      <c r="C43">
+        <v>190257696</v>
       </c>
       <c r="D43">
-        <v>40152678</v>
+        <v>198541438</v>
+      </c>
+      <c r="E43">
+        <v>36285035</v>
+      </c>
+      <c r="F43">
+        <v>122002089</v>
+      </c>
+      <c r="G43">
+        <v>81849411</v>
+      </c>
+      <c r="H43">
+        <v>52909752</v>
+      </c>
+      <c r="I43">
+        <v>69696678</v>
       </c>
     </row>
     <row r="44">
@@ -2344,26 +2164,71 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>11422869</v>
+        <v>-40830850</v>
+      </c>
+      <c r="C46">
+        <v>190257696</v>
       </c>
       <c r="D46">
-        <v>41234948</v>
+        <v>178834827</v>
+      </c>
+      <c r="E46">
+        <v>36285035</v>
+      </c>
+      <c r="F46">
+        <v>122002089</v>
+      </c>
+      <c r="G46">
+        <v>80767141</v>
+      </c>
+      <c r="H46">
+        <v>52909752</v>
+      </c>
+      <c r="I46">
+        <v>69696678</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>11422869</v>
+        <v>-40830850</v>
+      </c>
+      <c r="C48">
+        <v>190257696</v>
       </c>
       <c r="D48">
-        <v>41234948</v>
+        <v>178834827</v>
+      </c>
+      <c r="E48">
+        <v>36285035</v>
+      </c>
+      <c r="F48">
+        <v>122002089</v>
+      </c>
+      <c r="G48">
+        <v>80767141</v>
+      </c>
+      <c r="H48">
+        <v>52909752</v>
+      </c>
+      <c r="I48">
+        <v>69696678</v>
       </c>
     </row>
     <row r="49"/>
@@ -2372,22 +2237,40 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>43816390</v>
+        <v>42110846</v>
+      </c>
+      <c r="C50">
+        <v>155543420</v>
       </c>
       <c r="D50">
-        <v>157667909</v>
+        <v>111727030</v>
+      </c>
+      <c r="E50">
+        <v>34497793</v>
+      </c>
+      <c r="F50">
+        <v>237253862</v>
+      </c>
+      <c r="G50">
+        <v>79585953</v>
+      </c>
+      <c r="H50">
+        <v>84819402</v>
+      </c>
+      <c r="I50">
+        <v>55472384</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2396,6 +2279,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2403,21 +2288,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2431,19 +2322,16 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>448686813</v>
+        <v>51818936</v>
       </c>
       <c r="C3">
-        <v>426559658</v>
-      </c>
-      <c r="D3">
-        <v>345482207</v>
+        <v>102105275</v>
+      </c>
+      <c r="E3">
+        <v>67266312</v>
       </c>
       <c r="F3">
-        <v>287515179</v>
-      </c>
-      <c r="G3">
-        <v>178947454</v>
+        <v>79978120</v>
       </c>
     </row>
     <row r="4">
@@ -2466,19 +2354,16 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-323651484</v>
+        <v>-76560889</v>
       </c>
       <c r="C7">
-        <v>-354145398</v>
-      </c>
-      <c r="D7">
-        <v>-257480356</v>
+        <v>-77155611</v>
+      </c>
+      <c r="E7">
+        <v>-59848344</v>
       </c>
       <c r="F7">
-        <v>-188330683</v>
-      </c>
-      <c r="G7">
-        <v>-81596607</v>
+        <v>-107649525</v>
       </c>
     </row>
     <row r="8">
@@ -2486,35 +2371,50 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>125035329</v>
+        <v>-24741953</v>
       </c>
       <c r="C8">
-        <v>72414260</v>
-      </c>
-      <c r="D8">
-        <v>88001851</v>
+        <v>24949664</v>
+      </c>
+      <c r="E8">
+        <v>7417968</v>
       </c>
       <c r="F8">
-        <v>99184496</v>
-      </c>
-      <c r="G8">
-        <v>97350847</v>
+        <v>-27671405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2526,19 +2426,16 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>125035329</v>
+        <v>-24741953</v>
       </c>
       <c r="C13">
-        <v>72414260</v>
-      </c>
-      <c r="D13">
-        <v>88001851</v>
+        <v>24949664</v>
+      </c>
+      <c r="E13">
+        <v>7417968</v>
       </c>
       <c r="F13">
-        <v>99184496</v>
-      </c>
-      <c r="G13">
-        <v>97350847</v>
+        <v>-27671405</v>
       </c>
     </row>
     <row r="14"/>
@@ -2547,19 +2444,16 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-18658866</v>
+        <v>-23130813</v>
       </c>
       <c r="C15">
-        <v>-30968678</v>
-      </c>
-      <c r="D15">
-        <v>-25065759</v>
+        <v>-5963632</v>
+      </c>
+      <c r="E15">
+        <v>-2770069</v>
       </c>
       <c r="F15">
-        <v>-15872106</v>
-      </c>
-      <c r="G15">
-        <v>-10691285</v>
+        <v>-18273444</v>
       </c>
     </row>
     <row r="16">
@@ -2577,19 +2471,16 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>2679624</v>
+        <v>412034</v>
       </c>
       <c r="C18">
-        <v>1042705</v>
-      </c>
-      <c r="D18">
-        <v>2622648</v>
+        <v>-84772</v>
+      </c>
+      <c r="E18">
+        <v>17303662</v>
       </c>
       <c r="F18">
-        <v>6058934</v>
-      </c>
-      <c r="G18">
-        <v>10801617</v>
+        <v>-1721691</v>
       </c>
     </row>
     <row r="19">
@@ -2597,19 +2488,16 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-15373582</v>
+        <v>-3598962</v>
       </c>
       <c r="C19">
-        <v>-10875496</v>
-      </c>
-      <c r="D19">
-        <v>-2840412</v>
+        <v>1647363</v>
+      </c>
+      <c r="E19">
+        <v>-973496</v>
       </c>
       <c r="F19">
-        <v>-878099</v>
-      </c>
-      <c r="G19">
-        <v>-4621841</v>
+        <v>6145449</v>
       </c>
     </row>
     <row r="20">
@@ -2622,19 +2510,16 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>93682505</v>
+        <v>-51059694</v>
       </c>
       <c r="C21">
-        <v>31612791</v>
-      </c>
-      <c r="D21">
-        <v>62718328</v>
+        <v>20548623</v>
+      </c>
+      <c r="E21">
+        <v>20978065</v>
       </c>
       <c r="F21">
-        <v>88493225</v>
-      </c>
-      <c r="G21">
-        <v>92839338</v>
+        <v>-41521091</v>
       </c>
     </row>
     <row r="22"/>
@@ -2652,20 +2537,14 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="F25">
-        <v>1281157</v>
-      </c>
-      <c r="G25">
-        <v>6272173</v>
+      <c r="B25">
+        <v>25647509</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="F26">
-        <v>-19680306</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2702,19 +2581,16 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>93682505</v>
+        <v>-25412185</v>
       </c>
       <c r="C33">
-        <v>31612791</v>
-      </c>
-      <c r="D33">
-        <v>62718328</v>
+        <v>20548623</v>
+      </c>
+      <c r="E33">
+        <v>20978065</v>
       </c>
       <c r="F33">
-        <v>70094076</v>
-      </c>
-      <c r="G33">
-        <v>99111511</v>
+        <v>-41521091</v>
       </c>
     </row>
     <row r="34"/>
@@ -2723,19 +2599,16 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>226241670</v>
+        <v>5612971</v>
       </c>
       <c r="C35">
-        <v>252903775</v>
-      </c>
-      <c r="D35">
-        <v>129246505</v>
+        <v>62976266</v>
+      </c>
+      <c r="E35">
+        <v>54248589</v>
       </c>
       <c r="F35">
-        <v>213370889</v>
-      </c>
-      <c r="G35">
-        <v>161654973</v>
+        <v>89638371</v>
       </c>
     </row>
     <row r="36">
@@ -2743,44 +2616,41 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-72684977</v>
+        <v>-58577736</v>
       </c>
       <c r="C36">
-        <v>-63208299</v>
-      </c>
-      <c r="D36">
-        <v>-87348593</v>
+        <v>-34827129</v>
+      </c>
+      <c r="E36">
+        <v>-52909462</v>
       </c>
       <c r="F36">
-        <v>-245531920</v>
-      </c>
-      <c r="G36">
-        <v>-191427919</v>
+        <v>-25350451</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>30491</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>247239198</v>
+        <v>-78346459</v>
       </c>
       <c r="C38">
-        <v>221308267</v>
-      </c>
-      <c r="D38">
-        <v>104616240</v>
+        <v>48697760</v>
+      </c>
+      <c r="E38">
+        <v>22317192</v>
       </c>
       <c r="F38">
-        <v>37933045</v>
-      </c>
-      <c r="G38">
-        <v>69338565</v>
+        <v>22766829</v>
       </c>
     </row>
     <row r="39"/>
@@ -2789,44 +2659,32 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-56981502</v>
-      </c>
-      <c r="D40">
-        <v>17385849</v>
-      </c>
-      <c r="F40">
-        <v>14976707</v>
-      </c>
-      <c r="G40">
-        <v>358113</v>
+        <v>37515609</v>
+      </c>
+      <c r="E40">
+        <v>13967843</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="G41">
-        <v>-33</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-56981502</v>
+        <v>37515609</v>
       </c>
       <c r="C42">
-        <v>-1238492</v>
-      </c>
-      <c r="D42">
-        <v>17385849</v>
+        <v>-37274891</v>
+      </c>
+      <c r="E42">
+        <v>13967843</v>
       </c>
       <c r="F42">
-        <v>14976707</v>
-      </c>
-      <c r="G42">
-        <v>358080</v>
+        <v>18468119</v>
       </c>
     </row>
     <row r="43">
@@ -2834,19 +2692,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>190257696</v>
+        <v>-40830850</v>
       </c>
       <c r="C43">
-        <v>238694116</v>
-      </c>
-      <c r="D43">
-        <v>122002089</v>
+        <v>-8283742</v>
+      </c>
+      <c r="E43">
+        <v>36285035</v>
       </c>
       <c r="F43">
-        <v>52909752</v>
-      </c>
-      <c r="G43">
-        <v>69696678</v>
+        <v>40152678</v>
       </c>
     </row>
     <row r="44">
@@ -2860,19 +2715,16 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>190257696</v>
+        <v>-40830850</v>
       </c>
       <c r="C46">
-        <v>220069775</v>
-      </c>
-      <c r="D46">
-        <v>122002089</v>
+        <v>11422869</v>
+      </c>
+      <c r="E46">
+        <v>36285035</v>
       </c>
       <c r="F46">
-        <v>52909752</v>
-      </c>
-      <c r="G46">
-        <v>69696678</v>
+        <v>41234948</v>
       </c>
     </row>
     <row r="47">
@@ -2882,25 +2734,25 @@
       <c r="B47">
         <v>0</v>
       </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>190257696</v>
+        <v>-40830850</v>
       </c>
       <c r="C48">
-        <v>220069775</v>
-      </c>
-      <c r="D48">
-        <v>122002089</v>
+        <v>11422869</v>
+      </c>
+      <c r="E48">
+        <v>36285035</v>
       </c>
       <c r="F48">
-        <v>52909752</v>
-      </c>
-      <c r="G48">
-        <v>69696678</v>
+        <v>41234948</v>
       </c>
     </row>
     <row r="49"/>
@@ -2909,31 +2761,28 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>155543420</v>
+        <v>42110846</v>
       </c>
       <c r="C50">
-        <v>269394939</v>
-      </c>
-      <c r="D50">
-        <v>237253862</v>
+        <v>43816390</v>
+      </c>
+      <c r="E50">
+        <v>34497793</v>
       </c>
       <c r="F50">
-        <v>84819402</v>
-      </c>
-      <c r="G50">
-        <v>55472384</v>
+        <v>157667909</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2942,6 +2791,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2949,21 +2800,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2974,1115 +2831,569 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
+        <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>286120396</v>
+        <v>433239437</v>
       </c>
       <c r="C3">
-        <v>202341570</v>
+        <v>448686813</v>
       </c>
       <c r="D3">
-        <v>376692638</v>
-      </c>
-      <c r="E3">
-        <v>-249981083</v>
+        <v>426559658</v>
       </c>
       <c r="F3">
-        <v>186927659</v>
-      </c>
-      <c r="G3">
-        <v>144911674</v>
+        <v>345482207</v>
+      </c>
+      <c r="H3">
+        <v>287515179</v>
+      </c>
+      <c r="I3">
+        <v>178947454</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
-      </c>
-      <c r="B4">
-        <v>190257696</v>
-      </c>
-      <c r="C4">
-        <v>178834827</v>
-      </c>
-      <c r="D4">
-        <v>122002089</v>
-      </c>
-      <c r="E4">
-        <v>80767141</v>
-      </c>
-      <c r="F4">
-        <v>52909752</v>
-      </c>
-      <c r="G4">
-        <v>69696677</v>
+        <v xml:space="preserve">    Toplam Hasılat</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B5">
-        <v>127844046</v>
-      </c>
-      <c r="C5">
-        <v>54600893</v>
-      </c>
-      <c r="D5">
-        <v>250373687</v>
-      </c>
-      <c r="E5">
-        <v>-331228190</v>
-      </c>
-      <c r="F5">
-        <v>136533277</v>
-      </c>
-      <c r="G5">
-        <v>70647067</v>
+        <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B6">
-        <v>155543420</v>
-      </c>
-      <c r="C6">
-        <v>111727030</v>
-      </c>
-      <c r="D6">
-        <v>237253862</v>
-      </c>
-      <c r="E6">
-        <v>79585953</v>
-      </c>
-      <c r="F6">
-        <v>84819402</v>
-      </c>
-      <c r="G6">
-        <v>55472384</v>
+        <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>-340364029</v>
+      </c>
+      <c r="C7">
+        <v>-323651484</v>
+      </c>
+      <c r="D7">
+        <v>-354145398</v>
+      </c>
+      <c r="F7">
+        <v>-257480356</v>
+      </c>
+      <c r="H7">
+        <v>-188330683</v>
+      </c>
+      <c r="I7">
+        <v>-81596607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1997373</v>
+        <v>92875408</v>
       </c>
       <c r="C8">
-        <v>2132705</v>
+        <v>125035329</v>
       </c>
       <c r="D8">
-        <v>1085016</v>
-      </c>
-      <c r="E8">
-        <v>614232</v>
+        <v>72414260</v>
       </c>
       <c r="F8">
-        <v>302668</v>
-      </c>
-      <c r="G8">
-        <v>121363</v>
+        <v>88001851</v>
+      </c>
+      <c r="H8">
+        <v>99184496</v>
+      </c>
+      <c r="I8">
+        <v>97350847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B12">
-        <v>132536873</v>
-      </c>
-      <c r="C12">
-        <v>-36891541</v>
-      </c>
-      <c r="D12">
-        <v>-5272151</v>
-      </c>
-      <c r="E12">
-        <v>38586220</v>
-      </c>
-      <c r="F12">
-        <v>-2054919</v>
-      </c>
-      <c r="G12">
-        <v>-1530385</v>
+        <v xml:space="preserve">    Canlı Varlıklar Gerçeğe Uygun Değer Farkları</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Brüt Kar (Zarar)</v>
+      </c>
+      <c r="B13">
+        <v>92875408</v>
+      </c>
+      <c r="C13">
+        <v>125035329</v>
+      </c>
+      <c r="D13">
+        <v>72414260</v>
+      </c>
+      <c r="F13">
+        <v>88001851</v>
+      </c>
+      <c r="H13">
+        <v>99184496</v>
+      </c>
+      <c r="I13">
+        <v>97350847</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-350298446</v>
+        <v>-39019610</v>
       </c>
       <c r="C15">
-        <v>-45209700</v>
+        <v>-18658866</v>
       </c>
       <c r="D15">
-        <v>-53370186</v>
-      </c>
-      <c r="E15">
-        <v>-44882094</v>
+        <v>-30968678</v>
       </c>
       <c r="F15">
-        <v>-3495728</v>
-      </c>
-      <c r="G15">
-        <v>-40750112</v>
+        <v>-25065759</v>
+      </c>
+      <c r="H15">
+        <v>-15872106</v>
+      </c>
+      <c r="I15">
+        <v>-10691285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
+      </c>
+      <c r="B18">
+        <v>-14212004</v>
+      </c>
+      <c r="C18">
+        <v>2679624</v>
+      </c>
+      <c r="D18">
+        <v>1042705</v>
+      </c>
+      <c r="F18">
+        <v>2622648</v>
+      </c>
+      <c r="H18">
+        <v>6058934</v>
+      </c>
+      <c r="I18">
+        <v>10801617</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
+      </c>
+      <c r="B19">
+        <v>-17999048</v>
+      </c>
+      <c r="C19">
+        <v>-15373582</v>
+      </c>
+      <c r="D19">
+        <v>-10875496</v>
+      </c>
+      <c r="F19">
+        <v>-2840412</v>
+      </c>
+      <c r="H19">
+        <v>-878099</v>
+      </c>
+      <c r="I19">
+        <v>-4621841</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B20">
-        <v>188064826</v>
-      </c>
-      <c r="C20">
-        <v>19706611</v>
-      </c>
-      <c r="D20">
-        <v>-17385849</v>
-      </c>
-      <c r="E20">
-        <v>75989939</v>
-      </c>
-      <c r="F20">
-        <v>-14976707</v>
-      </c>
-      <c r="G20">
-        <v>-358113</v>
+        <v xml:space="preserve">    Diğer Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="G22">
-        <v>-635973</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B21">
+        <v>21644746</v>
+      </c>
+      <c r="C21">
+        <v>93682505</v>
+      </c>
+      <c r="D21">
+        <v>31612791</v>
+      </c>
+      <c r="F21">
+        <v>62718328</v>
+      </c>
+      <c r="H21">
+        <v>88493225</v>
+      </c>
+      <c r="I21">
+        <v>92839338</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ödenecek Kar Paylarının Defter Değeri ile Dağıtılan Nakit Dışı Varlıkların Değeri Arasındaki Fark</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Finansal Tablo Dışı Bırakılmasından Kaynaklanan Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
+      </c>
+      <c r="H25">
+        <v>1281157</v>
+      </c>
+      <c r="I25">
+        <v>6272173</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
+      </c>
+      <c r="H26">
+        <v>-19680306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
+        <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
-      </c>
-      <c r="B28">
-        <v>-31981346</v>
-      </c>
-      <c r="C28">
-        <v>-31094150</v>
-      </c>
-      <c r="D28">
-        <v>4316862</v>
-      </c>
-      <c r="E28">
-        <v>479966</v>
-      </c>
-      <c r="F28">
-        <v>-2515370</v>
-      </c>
-      <c r="G28">
-        <v>4567930</v>
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
-      </c>
-      <c r="B29">
-        <v>-580444</v>
+        <v xml:space="preserve">    İştirakler, Müşterek Kontrol Edilen İşletmeler ve Bağlı Ortaklıklardan Diğer Gelirler (Giderler)</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabındaki Azalış (Artış)</v>
+        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
-      </c>
-      <c r="B31">
-        <v>-17667689</v>
-      </c>
-      <c r="C31">
-        <v>-48888164</v>
-      </c>
-      <c r="D31">
-        <v>5792801</v>
-      </c>
-      <c r="E31">
-        <v>-36438279</v>
-      </c>
-      <c r="F31">
-        <v>-3795052</v>
-      </c>
-      <c r="G31">
-        <v>-1991389</v>
+        <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
+        <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>558666</v>
+        <v>47292255</v>
       </c>
       <c r="C33">
-        <v>1188309</v>
+        <v>93682505</v>
       </c>
       <c r="D33">
-        <v>8017380</v>
-      </c>
-      <c r="E33">
-        <v>-175809</v>
+        <v>31612791</v>
       </c>
       <c r="F33">
-        <v>7520321</v>
-      </c>
-      <c r="G33">
-        <v>6327903</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v>62718328</v>
+      </c>
+      <c r="H33">
+        <v>70094076</v>
+      </c>
+      <c r="I33">
+        <v>99111511</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
+      </c>
+      <c r="B35">
+        <v>177606052</v>
+      </c>
+      <c r="C35">
+        <v>226241670</v>
+      </c>
+      <c r="D35">
+        <v>252903775</v>
+      </c>
+      <c r="F35">
+        <v>129246505</v>
+      </c>
+      <c r="H35">
+        <v>213370889</v>
+      </c>
+      <c r="I35">
+        <v>161654973</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
+      </c>
+      <c r="B36">
+        <v>-78353251</v>
+      </c>
+      <c r="C36">
+        <v>-72684977</v>
+      </c>
+      <c r="D36">
+        <v>-63208299</v>
+      </c>
+      <c r="F36">
+        <v>-87348593</v>
+      </c>
+      <c r="H36">
+        <v>-245531920</v>
+      </c>
+      <c r="I36">
+        <v>-191427919</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    Canlı Varlıklardaki Azalış (Artış)</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
-      </c>
-      <c r="B39">
-        <v>-149247</v>
-      </c>
-      <c r="C39">
-        <v>-413230</v>
-      </c>
-      <c r="D39">
-        <v>173131</v>
-      </c>
-      <c r="E39">
-        <v>-549286</v>
-      </c>
-      <c r="F39">
-        <v>-391821</v>
-      </c>
-      <c r="G39">
-        <v>-2059531</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
+      </c>
+      <c r="B38">
+        <v>146575547</v>
+      </c>
+      <c r="C38">
+        <v>247239198</v>
+      </c>
+      <c r="D38">
+        <v>221308267</v>
+      </c>
+      <c r="F38">
+        <v>104616240</v>
+      </c>
+      <c r="H38">
+        <v>37933045</v>
+      </c>
+      <c r="I38">
+        <v>69338565</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>3044747</v>
+        <v>-33433736</v>
       </c>
       <c r="C40">
-        <v>19286877</v>
-      </c>
-      <c r="D40">
-        <v>11078107</v>
-      </c>
-      <c r="E40">
-        <v>20489809</v>
+        <v>-56981502</v>
       </c>
       <c r="F40">
-        <v>2178340</v>
-      </c>
-      <c r="G40">
-        <v>-8448033</v>
+        <v>17385849</v>
+      </c>
+      <c r="H40">
+        <v>14976707</v>
+      </c>
+      <c r="I40">
+        <v>358113</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
+      </c>
+      <c r="I41">
+        <v>-33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>245931</v>
+        <v>-33433736</v>
       </c>
       <c r="C42">
-        <v>1172342</v>
+        <v>-56981502</v>
       </c>
       <c r="D42">
-        <v>658208</v>
-      </c>
-      <c r="E42">
-        <v>6117882</v>
+        <v>-1238492</v>
       </c>
       <c r="F42">
-        <v>829207</v>
-      </c>
-      <c r="G42">
-        <v>-476087</v>
+        <v>17385849</v>
+      </c>
+      <c r="H42">
+        <v>14976707</v>
+      </c>
+      <c r="I42">
+        <v>358080</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+      <c r="B43">
+        <v>113141811</v>
+      </c>
+      <c r="C43">
+        <v>190257696</v>
+      </c>
+      <c r="D43">
+        <v>238694116</v>
+      </c>
+      <c r="F43">
+        <v>122002089</v>
+      </c>
+      <c r="H43">
+        <v>52909752</v>
+      </c>
+      <c r="I43">
+        <v>69696678</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
-      </c>
-      <c r="B44">
-        <v>-17433310</v>
-      </c>
-      <c r="C44">
-        <v>-3703251</v>
-      </c>
-      <c r="D44">
-        <v>-498360</v>
-      </c>
-      <c r="E44">
-        <v>10830746</v>
-      </c>
-      <c r="F44">
-        <v>27661255</v>
-      </c>
-      <c r="G44">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v xml:space="preserve">    Türev Yükümlülüklerdeki Artış (Azalış)</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımlarındaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
+      </c>
+      <c r="B46">
+        <v>113141811</v>
+      </c>
+      <c r="C46">
+        <v>190257696</v>
+      </c>
+      <c r="D46">
+        <v>220069775</v>
+      </c>
+      <c r="F46">
+        <v>122002089</v>
+      </c>
+      <c r="H46">
+        <v>52909752</v>
+      </c>
+      <c r="I46">
+        <v>69696678</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
-      </c>
-      <c r="F47">
-        <v>-184625</v>
-      </c>
-      <c r="G47">
-        <v>-285236</v>
+        <v xml:space="preserve">    Azınlık Payları</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>113141811</v>
       </c>
       <c r="C48">
-        <v>-243235</v>
+        <v>190257696</v>
       </c>
       <c r="D48">
-        <v>-6234658</v>
-      </c>
-      <c r="E48">
-        <v>154903</v>
+        <v>220069775</v>
       </c>
       <c r="F48">
-        <v>-874625</v>
-      </c>
-      <c r="G48">
-        <v>1042626</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
-      </c>
-      <c r="B49">
-        <v>286120396</v>
-      </c>
-    </row>
+        <v>122002089</v>
+      </c>
+      <c r="H48">
+        <v>52909752</v>
+      </c>
+      <c r="I48">
+        <v>69696678</v>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v xml:space="preserve">    Kira Ödemeleri</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v xml:space="preserve">    Alınan Kira</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B67">
-        <v>-49204258</v>
-      </c>
-      <c r="C67">
-        <v>-43685954</v>
-      </c>
-      <c r="D67">
-        <v>-4865360</v>
-      </c>
-      <c r="E67">
-        <v>-1665315</v>
-      </c>
-      <c r="F67">
-        <v>109763</v>
-      </c>
-      <c r="G67">
-        <v>-163903</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B78">
-        <v>-49204258</v>
-      </c>
-      <c r="C78">
-        <v>-43685954</v>
-      </c>
-      <c r="D78">
-        <v>-157564738</v>
-      </c>
-      <c r="E78">
-        <v>-1665315</v>
-      </c>
-      <c r="F78">
-        <v>-5872001</v>
-      </c>
-      <c r="G78">
-        <v>-5972118</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B101">
-        <v>-164631344</v>
-      </c>
-      <c r="C101">
-        <v>-91153849</v>
-      </c>
-      <c r="D101">
-        <v>-230184273</v>
-      </c>
-      <c r="E101">
-        <v>47207479</v>
-      </c>
-      <c r="F101">
-        <v>-168788616</v>
-      </c>
-      <c r="G101">
-        <v>-140483941</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="E107">
-        <v>88525000</v>
-      </c>
-      <c r="F107">
-        <v>18816970</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B109">
-        <v>125000000</v>
-      </c>
-      <c r="C109">
-        <v>60000000</v>
-      </c>
-      <c r="D109">
-        <v>10000000</v>
-      </c>
-      <c r="E109">
-        <v>6951196</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B110">
-        <v>-237870260</v>
-      </c>
-      <c r="C110">
-        <v>-184909602</v>
-      </c>
-      <c r="D110">
-        <v>-198202238</v>
-      </c>
-      <c r="E110">
-        <v>-86854937</v>
-      </c>
-      <c r="F110">
-        <v>-144449911</v>
-      </c>
-      <c r="G110">
-        <v>-99622084</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B113">
-        <v>-3247231</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-      <c r="B118">
-        <v>-50405861</v>
-      </c>
-      <c r="C118">
-        <v>35323647</v>
-      </c>
-      <c r="D118">
-        <v>-52512446</v>
-      </c>
-      <c r="E118">
-        <v>42698578</v>
-      </c>
-      <c r="F118">
-        <v>-56322474</v>
-      </c>
-      <c r="G118">
-        <v>-42972564</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B119">
-        <v>1892008</v>
-      </c>
-      <c r="C119">
-        <v>-1567894</v>
-      </c>
-      <c r="D119">
-        <v>5074031</v>
-      </c>
-      <c r="E119">
-        <v>-4112358</v>
-      </c>
-      <c r="F119">
-        <v>1686799</v>
-      </c>
-      <c r="G119">
-        <v>965385</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B125">
-        <v>72284794</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
-      </c>
-      <c r="B126">
-        <v>-14752202</v>
-      </c>
-      <c r="C126">
-        <v>67501767</v>
-      </c>
-      <c r="E126">
-        <v>-204438919</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B127">
-        <v>57532592</v>
-      </c>
-      <c r="C127">
-        <v>-2623940</v>
-      </c>
-      <c r="D127">
-        <v>-11056373</v>
-      </c>
-      <c r="E127">
-        <v>-2137714</v>
-      </c>
-      <c r="F127">
-        <v>12267042</v>
-      </c>
-      <c r="G127">
-        <v>-1544385</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B128">
-        <v>11262460</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B129">
-        <v>68795052</v>
+        <v xml:space="preserve">    Amortisman</v>
+      </c>
+      <c r="B50">
+        <v>163156473</v>
+      </c>
+      <c r="C50">
+        <v>155543420</v>
+      </c>
+      <c r="D50">
+        <v>269394939</v>
+      </c>
+      <c r="F50">
+        <v>237253862</v>
+      </c>
+      <c r="H50">
+        <v>84819402</v>
+      </c>
+      <c r="I50">
+        <v>55472384</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4091,6 +3402,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4098,21 +3411,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -4126,10 +3445,28 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>83778826</v>
+        <v>13074643</v>
+      </c>
+      <c r="C3">
+        <v>286120396</v>
       </c>
       <c r="D3">
-        <v>626673721</v>
+        <v>202341570</v>
+      </c>
+      <c r="E3">
+        <v>49767187</v>
+      </c>
+      <c r="F3">
+        <v>376692638</v>
+      </c>
+      <c r="G3">
+        <v>-249981083</v>
+      </c>
+      <c r="H3">
+        <v>186927659</v>
+      </c>
+      <c r="I3">
+        <v>144911674</v>
       </c>
     </row>
     <row r="4">
@@ -4137,10 +3474,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>11422869</v>
+        <v>-40830850</v>
+      </c>
+      <c r="C4">
+        <v>190257696</v>
       </c>
       <c r="D4">
-        <v>41234948</v>
+        <v>178834827</v>
+      </c>
+      <c r="E4">
+        <v>36285035</v>
+      </c>
+      <c r="F4">
+        <v>122002089</v>
+      </c>
+      <c r="G4">
+        <v>80767141</v>
+      </c>
+      <c r="H4">
+        <v>52909752</v>
+      </c>
+      <c r="I4">
+        <v>69696677</v>
       </c>
     </row>
     <row r="5">
@@ -4148,10 +3503,28 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>73243153</v>
+        <v>47191923</v>
+      </c>
+      <c r="C5">
+        <v>127844046</v>
       </c>
       <c r="D5">
-        <v>581601877</v>
+        <v>54600893</v>
+      </c>
+      <c r="E5">
+        <v>46876595</v>
+      </c>
+      <c r="F5">
+        <v>250373687</v>
+      </c>
+      <c r="G5">
+        <v>-331228190</v>
+      </c>
+      <c r="H5">
+        <v>136533277</v>
+      </c>
+      <c r="I5">
+        <v>70647067</v>
       </c>
     </row>
     <row r="6">
@@ -4159,26 +3532,65 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>43816390</v>
+        <v>42110846</v>
+      </c>
+      <c r="C6">
+        <v>155543420</v>
       </c>
       <c r="D6">
-        <v>157667909</v>
+        <v>111727030</v>
+      </c>
+      <c r="E6">
+        <v>34497793</v>
+      </c>
+      <c r="F6">
+        <v>237253862</v>
+      </c>
+      <c r="G6">
+        <v>79585953</v>
+      </c>
+      <c r="H6">
+        <v>84819402</v>
+      </c>
+      <c r="I6">
+        <v>55472384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-135332</v>
+        <v>180292</v>
+      </c>
+      <c r="C8">
+        <v>1997373</v>
       </c>
       <c r="D8">
-        <v>470784</v>
+        <v>2132705</v>
+      </c>
+      <c r="E8">
+        <v>756813</v>
+      </c>
+      <c r="F8">
+        <v>1085016</v>
+      </c>
+      <c r="G8">
+        <v>614232</v>
+      </c>
+      <c r="H8">
+        <v>302668</v>
+      </c>
+      <c r="I8">
+        <v>121363</v>
       </c>
     </row>
     <row r="9">
@@ -4201,10 +3613,28 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>169428414</v>
+        <v>16113066</v>
+      </c>
+      <c r="C12">
+        <v>132536873</v>
       </c>
       <c r="D12">
-        <v>-43858371</v>
+        <v>-36891541</v>
+      </c>
+      <c r="E12">
+        <v>24944632</v>
+      </c>
+      <c r="F12">
+        <v>-5272151</v>
+      </c>
+      <c r="G12">
+        <v>38586220</v>
+      </c>
+      <c r="H12">
+        <v>-2054919</v>
+      </c>
+      <c r="I12">
+        <v>-1530385</v>
       </c>
     </row>
     <row r="13">
@@ -4221,11 +3651,23 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B15">
-        <v>-305088746</v>
+      <c r="C15">
+        <v>-350298446</v>
       </c>
       <c r="D15">
-        <v>-8488092</v>
+        <v>-45209700</v>
+      </c>
+      <c r="F15">
+        <v>-53370186</v>
+      </c>
+      <c r="G15">
+        <v>-44882094</v>
+      </c>
+      <c r="H15">
+        <v>-3495728</v>
+      </c>
+      <c r="I15">
+        <v>-40750112</v>
       </c>
     </row>
     <row r="16">
@@ -4253,10 +3695,28 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>168358215</v>
+        <v>-37515609</v>
+      </c>
+      <c r="C20">
+        <v>188064826</v>
       </c>
       <c r="D20">
-        <v>-93375788</v>
+        <v>19706611</v>
+      </c>
+      <c r="E20">
+        <v>-13967843</v>
+      </c>
+      <c r="F20">
+        <v>-17385849</v>
+      </c>
+      <c r="G20">
+        <v>75989939</v>
+      </c>
+      <c r="H20">
+        <v>-14976707</v>
+      </c>
+      <c r="I20">
+        <v>-358113</v>
       </c>
     </row>
     <row r="21">
@@ -4268,6 +3728,9 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="I22">
+        <v>-635973</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -4299,16 +3762,37 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-887196</v>
+        <v>6713570</v>
+      </c>
+      <c r="C28">
+        <v>-31981346</v>
       </c>
       <c r="D28">
-        <v>3836896</v>
+        <v>-31094150</v>
+      </c>
+      <c r="E28">
+        <v>-33394443</v>
+      </c>
+      <c r="F28">
+        <v>4316862</v>
+      </c>
+      <c r="G28">
+        <v>479966</v>
+      </c>
+      <c r="H28">
+        <v>-2515370</v>
+      </c>
+      <c r="I28">
+        <v>4567930</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="C29">
+        <v>-580444</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -4320,10 +3804,28 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>31220475</v>
+        <v>10857033</v>
+      </c>
+      <c r="C31">
+        <v>-17667689</v>
       </c>
       <c r="D31">
-        <v>42231080</v>
+        <v>-48888164</v>
+      </c>
+      <c r="E31">
+        <v>-25816082</v>
+      </c>
+      <c r="F31">
+        <v>5792801</v>
+      </c>
+      <c r="G31">
+        <v>-36438279</v>
+      </c>
+      <c r="H31">
+        <v>-3795052</v>
+      </c>
+      <c r="I31">
+        <v>-1991389</v>
       </c>
     </row>
     <row r="32">
@@ -4336,10 +3838,28 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-629643</v>
+        <v>-33579</v>
+      </c>
+      <c r="C33">
+        <v>558666</v>
       </c>
       <c r="D33">
-        <v>8193189</v>
+        <v>1188309</v>
+      </c>
+      <c r="E33">
+        <v>1275854</v>
+      </c>
+      <c r="F33">
+        <v>8017380</v>
+      </c>
+      <c r="G33">
+        <v>-175809</v>
+      </c>
+      <c r="H33">
+        <v>7520321</v>
+      </c>
+      <c r="I33">
+        <v>6327903</v>
       </c>
     </row>
     <row r="34">
@@ -4372,10 +3892,28 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>263983</v>
+        <v>-78356</v>
+      </c>
+      <c r="C39">
+        <v>-149247</v>
       </c>
       <c r="D39">
-        <v>722417</v>
+        <v>-413230</v>
+      </c>
+      <c r="E39">
+        <v>762184</v>
+      </c>
+      <c r="F39">
+        <v>173131</v>
+      </c>
+      <c r="G39">
+        <v>-549286</v>
+      </c>
+      <c r="H39">
+        <v>-391821</v>
+      </c>
+      <c r="I39">
+        <v>-2059531</v>
       </c>
     </row>
     <row r="40">
@@ -4383,26 +3921,68 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-16242130</v>
+        <v>-159478</v>
+      </c>
+      <c r="C40">
+        <v>3044747</v>
       </c>
       <c r="D40">
-        <v>-9411702</v>
+        <v>19286877</v>
+      </c>
+      <c r="E40">
+        <v>-587350</v>
+      </c>
+      <c r="F40">
+        <v>11078107</v>
+      </c>
+      <c r="G40">
+        <v>20489809</v>
+      </c>
+      <c r="H40">
+        <v>2178340</v>
+      </c>
+      <c r="I40">
+        <v>-8448033</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B41">
+        <v>-8197</v>
+      </c>
+      <c r="E41">
+        <v>-88491</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-926411</v>
+        <v>1924257</v>
+      </c>
+      <c r="C42">
+        <v>245931</v>
       </c>
       <c r="D42">
-        <v>-5459674</v>
+        <v>1172342</v>
+      </c>
+      <c r="E42">
+        <v>584100</v>
+      </c>
+      <c r="F42">
+        <v>658208</v>
+      </c>
+      <c r="G42">
+        <v>6117882</v>
+      </c>
+      <c r="H42">
+        <v>829207</v>
+      </c>
+      <c r="I42">
+        <v>-476087</v>
       </c>
     </row>
     <row r="43">
@@ -4415,10 +3995,28 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-13730059</v>
+        <v>-5787820</v>
+      </c>
+      <c r="C44">
+        <v>-17433310</v>
       </c>
       <c r="D44">
-        <v>-11329106</v>
+        <v>-3703251</v>
+      </c>
+      <c r="E44">
+        <v>-5207717</v>
+      </c>
+      <c r="F44">
+        <v>-498360</v>
+      </c>
+      <c r="G44">
+        <v>10830746</v>
+      </c>
+      <c r="H44">
+        <v>27661255</v>
+      </c>
+      <c r="I44">
+        <v>1887</v>
       </c>
     </row>
     <row r="45">
@@ -4435,21 +4033,54 @@
       <c r="A47" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
+      <c r="H47">
+        <v>-184625</v>
+      </c>
+      <c r="I47">
+        <v>-285236</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>243235</v>
+        <v>-290</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>-6389561</v>
+        <v>-243235</v>
+      </c>
+      <c r="E48">
+        <v>-4316941</v>
+      </c>
+      <c r="F48">
+        <v>-6234658</v>
+      </c>
+      <c r="G48">
+        <v>154903</v>
+      </c>
+      <c r="H48">
+        <v>-874625</v>
+      </c>
+      <c r="I48">
+        <v>1042626</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
+      </c>
+      <c r="B49">
+        <v>13074643</v>
+      </c>
+      <c r="C49">
+        <v>286120396</v>
+      </c>
+      <c r="E49">
+        <v>49767187</v>
       </c>
     </row>
     <row r="50">
@@ -4538,10 +4169,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-5518304</v>
+        <v>-533599839</v>
+      </c>
+      <c r="C67">
+        <v>-49204258</v>
       </c>
       <c r="D67">
-        <v>-3200045</v>
+        <v>-43685954</v>
+      </c>
+      <c r="E67">
+        <v>-16659266</v>
+      </c>
+      <c r="F67">
+        <v>-4865360</v>
+      </c>
+      <c r="G67">
+        <v>-1665315</v>
+      </c>
+      <c r="H67">
+        <v>109763</v>
+      </c>
+      <c r="I67">
+        <v>-163903</v>
       </c>
     </row>
     <row r="68">
@@ -4588,6 +4237,9 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="B76">
+        <v>-533378718</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4599,10 +4251,28 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-5518304</v>
+        <v>-221121</v>
+      </c>
+      <c r="C78">
+        <v>-49204258</v>
       </c>
       <c r="D78">
-        <v>-155899423</v>
+        <v>-43685954</v>
+      </c>
+      <c r="E78">
+        <v>-16659266</v>
+      </c>
+      <c r="F78">
+        <v>-157564738</v>
+      </c>
+      <c r="G78">
+        <v>-1665315</v>
+      </c>
+      <c r="H78">
+        <v>-5872001</v>
+      </c>
+      <c r="I78">
+        <v>-5972118</v>
       </c>
     </row>
     <row r="79">
@@ -4716,10 +4386,28 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-73477495</v>
+        <v>500126481</v>
+      </c>
+      <c r="C101">
+        <v>-164631344</v>
       </c>
       <c r="D101">
-        <v>-277391752</v>
+        <v>-91153849</v>
+      </c>
+      <c r="E101">
+        <v>-22715601</v>
+      </c>
+      <c r="F101">
+        <v>-230184273</v>
+      </c>
+      <c r="G101">
+        <v>47207479</v>
+      </c>
+      <c r="H101">
+        <v>-168788616</v>
+      </c>
+      <c r="I101">
+        <v>-140483941</v>
       </c>
     </row>
     <row r="102">
@@ -4736,6 +4424,12 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B104">
+        <v>544447675</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4751,6 +4445,12 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="G107">
+        <v>88525000</v>
+      </c>
+      <c r="H107">
+        <v>18816970</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -4762,10 +4462,22 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>65000000</v>
+        <v>50000000</v>
+      </c>
+      <c r="C109">
+        <v>125000000</v>
       </c>
       <c r="D109">
-        <v>3048804</v>
+        <v>60000000</v>
+      </c>
+      <c r="E109">
+        <v>50000000</v>
+      </c>
+      <c r="F109">
+        <v>10000000</v>
+      </c>
+      <c r="G109">
+        <v>6951196</v>
       </c>
     </row>
     <row r="110">
@@ -4773,10 +4485,28 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-52960658</v>
+        <v>-77526539</v>
+      </c>
+      <c r="C110">
+        <v>-237870260</v>
       </c>
       <c r="D110">
-        <v>-111347301</v>
+        <v>-184909602</v>
+      </c>
+      <c r="E110">
+        <v>-53450798</v>
+      </c>
+      <c r="F110">
+        <v>-198202238</v>
+      </c>
+      <c r="G110">
+        <v>-86854937</v>
+      </c>
+      <c r="H110">
+        <v>-144449911</v>
+      </c>
+      <c r="I110">
+        <v>-99622084</v>
       </c>
     </row>
     <row r="111">
@@ -4793,6 +4523,15 @@
       <c r="A113" t="str">
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
+      <c r="B113">
+        <v>-2293451</v>
+      </c>
+      <c r="C113">
+        <v>-3247231</v>
+      </c>
+      <c r="E113">
+        <v>3648569</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4819,10 +4558,28 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-85729508</v>
+        <v>-15042330</v>
+      </c>
+      <c r="C118">
+        <v>-50405861</v>
       </c>
       <c r="D118">
-        <v>-95211024</v>
+        <v>35323647</v>
+      </c>
+      <c r="E118">
+        <v>-23156366</v>
+      </c>
+      <c r="F118">
+        <v>-52512446</v>
+      </c>
+      <c r="G118">
+        <v>42698578</v>
+      </c>
+      <c r="H118">
+        <v>-56322474</v>
+      </c>
+      <c r="I118">
+        <v>-42972564</v>
       </c>
     </row>
     <row r="119">
@@ -4830,10 +4587,28 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>3459902</v>
+        <v>541126</v>
+      </c>
+      <c r="C119">
+        <v>1892008</v>
       </c>
       <c r="D119">
-        <v>9186389</v>
+        <v>-1567894</v>
+      </c>
+      <c r="E119">
+        <v>242994</v>
+      </c>
+      <c r="F119">
+        <v>5074031</v>
+      </c>
+      <c r="G119">
+        <v>-4112358</v>
+      </c>
+      <c r="H119">
+        <v>1686799</v>
+      </c>
+      <c r="I119">
+        <v>965385</v>
       </c>
     </row>
     <row r="120">
@@ -4865,13 +4640,34 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
+      <c r="B125">
+        <v>-20398715</v>
+      </c>
+      <c r="C125">
+        <v>72284794</v>
+      </c>
+      <c r="E125">
+        <v>10392320</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-82253969</v>
+        <v>-1690097</v>
+      </c>
+      <c r="C126">
+        <v>-14752202</v>
+      </c>
+      <c r="D126">
+        <v>67501767</v>
+      </c>
+      <c r="E126">
+        <v>-1425070</v>
+      </c>
+      <c r="G126">
+        <v>-204438919</v>
       </c>
     </row>
     <row r="127">
@@ -4879,32 +4675,68 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>60156532</v>
+        <v>-22088812</v>
+      </c>
+      <c r="C127">
+        <v>57532592</v>
       </c>
       <c r="D127">
-        <v>-8918659</v>
+        <v>-2623940</v>
+      </c>
+      <c r="E127">
+        <v>8967250</v>
+      </c>
+      <c r="F127">
+        <v>-11056373</v>
+      </c>
+      <c r="G127">
+        <v>-2137714</v>
+      </c>
+      <c r="H127">
+        <v>12267042</v>
+      </c>
+      <c r="I127">
+        <v>-1544385</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B128">
+        <v>68795052</v>
+      </c>
+      <c r="C128">
+        <v>11262460</v>
+      </c>
+      <c r="E128">
+        <v>11262460</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B129">
+        <v>46706240</v>
+      </c>
+      <c r="C129">
+        <v>68795052</v>
+      </c>
+      <c r="E129">
+        <v>20229710</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4913,6 +4745,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4920,21 +4754,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -4948,19 +4788,16 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>286120396</v>
+        <v>13074643</v>
       </c>
       <c r="C3">
-        <v>829015291</v>
-      </c>
-      <c r="D3">
-        <v>376692638</v>
+        <v>83778826</v>
+      </c>
+      <c r="E3">
+        <v>49767187</v>
       </c>
       <c r="F3">
-        <v>186927659</v>
-      </c>
-      <c r="G3">
-        <v>144911674</v>
+        <v>626673721</v>
       </c>
     </row>
     <row r="4">
@@ -4968,19 +4805,16 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>190257696</v>
+        <v>-40830850</v>
       </c>
       <c r="C4">
-        <v>220069775</v>
-      </c>
-      <c r="D4">
-        <v>122002089</v>
+        <v>11422869</v>
+      </c>
+      <c r="E4">
+        <v>36285035</v>
       </c>
       <c r="F4">
-        <v>52909752</v>
-      </c>
-      <c r="G4">
-        <v>69696677</v>
+        <v>41234948</v>
       </c>
     </row>
     <row r="5">
@@ -4988,19 +4822,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>127844046</v>
+        <v>47191923</v>
       </c>
       <c r="C5">
-        <v>636202770</v>
-      </c>
-      <c r="D5">
-        <v>250373687</v>
+        <v>73243153</v>
+      </c>
+      <c r="E5">
+        <v>46876595</v>
       </c>
       <c r="F5">
-        <v>136533277</v>
-      </c>
-      <c r="G5">
-        <v>70647067</v>
+        <v>581601877</v>
       </c>
     </row>
     <row r="6">
@@ -5008,47 +4839,38 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>155543420</v>
+        <v>42110846</v>
       </c>
       <c r="C6">
-        <v>269394939</v>
-      </c>
-      <c r="D6">
-        <v>237253862</v>
+        <v>43816390</v>
+      </c>
+      <c r="E6">
+        <v>34497793</v>
       </c>
       <c r="F6">
-        <v>84819402</v>
-      </c>
-      <c r="G6">
-        <v>55472384</v>
+        <v>157667909</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1997373</v>
+        <v>180292</v>
       </c>
       <c r="C8">
-        <v>2603489</v>
-      </c>
-      <c r="D8">
-        <v>1085016</v>
+        <v>-135332</v>
+      </c>
+      <c r="E8">
+        <v>756813</v>
       </c>
       <c r="F8">
-        <v>302668</v>
-      </c>
-      <c r="G8">
-        <v>121363</v>
+        <v>470784</v>
       </c>
     </row>
     <row r="9">
@@ -5071,19 +4893,16 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>132536873</v>
+        <v>16113066</v>
       </c>
       <c r="C12">
-        <v>-80749912</v>
-      </c>
-      <c r="D12">
-        <v>-5272151</v>
+        <v>169428414</v>
+      </c>
+      <c r="E12">
+        <v>24944632</v>
       </c>
       <c r="F12">
-        <v>-2054919</v>
-      </c>
-      <c r="G12">
-        <v>-1530385</v>
+        <v>-43858371</v>
       </c>
     </row>
     <row r="13">
@@ -5100,20 +4919,11 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B15">
-        <v>-350298446</v>
-      </c>
       <c r="C15">
-        <v>-53697792</v>
-      </c>
-      <c r="D15">
-        <v>-53370186</v>
+        <v>-305088746</v>
       </c>
       <c r="F15">
-        <v>-3495728</v>
-      </c>
-      <c r="G15">
-        <v>-40750112</v>
+        <v>-8488092</v>
       </c>
     </row>
     <row r="16">
@@ -5141,19 +4951,16 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>188064826</v>
+        <v>-37515609</v>
       </c>
       <c r="C20">
-        <v>-73669177</v>
-      </c>
-      <c r="D20">
-        <v>-17385849</v>
+        <v>168358215</v>
+      </c>
+      <c r="E20">
+        <v>-13967843</v>
       </c>
       <c r="F20">
-        <v>-14976707</v>
-      </c>
-      <c r="G20">
-        <v>-358113</v>
+        <v>-93375788</v>
       </c>
     </row>
     <row r="21">
@@ -5165,9 +4972,6 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="G22">
-        <v>-635973</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -5199,28 +5003,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-31981346</v>
+        <v>6713570</v>
       </c>
       <c r="C28">
-        <v>-27257254</v>
-      </c>
-      <c r="D28">
-        <v>4316862</v>
+        <v>-887196</v>
+      </c>
+      <c r="E28">
+        <v>-33394443</v>
       </c>
       <c r="F28">
-        <v>-2515370</v>
-      </c>
-      <c r="G28">
-        <v>4567930</v>
+        <v>3836896</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="B29">
-        <v>-580444</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -5232,19 +5030,16 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-17667689</v>
+        <v>10857033</v>
       </c>
       <c r="C31">
-        <v>-6657084</v>
-      </c>
-      <c r="D31">
-        <v>5792801</v>
+        <v>31220475</v>
+      </c>
+      <c r="E31">
+        <v>-25816082</v>
       </c>
       <c r="F31">
-        <v>-3795052</v>
-      </c>
-      <c r="G31">
-        <v>-1991389</v>
+        <v>42231080</v>
       </c>
     </row>
     <row r="32">
@@ -5257,19 +5052,16 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>558666</v>
+        <v>-33579</v>
       </c>
       <c r="C33">
-        <v>9381498</v>
-      </c>
-      <c r="D33">
-        <v>8017380</v>
+        <v>-629643</v>
+      </c>
+      <c r="E33">
+        <v>1275854</v>
       </c>
       <c r="F33">
-        <v>7520321</v>
-      </c>
-      <c r="G33">
-        <v>6327903</v>
+        <v>8193189</v>
       </c>
     </row>
     <row r="34">
@@ -5302,19 +5094,16 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-149247</v>
+        <v>-78356</v>
       </c>
       <c r="C39">
-        <v>309187</v>
-      </c>
-      <c r="D39">
-        <v>173131</v>
+        <v>263983</v>
+      </c>
+      <c r="E39">
+        <v>762184</v>
       </c>
       <c r="F39">
-        <v>-391821</v>
-      </c>
-      <c r="G39">
-        <v>-2059531</v>
+        <v>722417</v>
       </c>
     </row>
     <row r="40">
@@ -5322,44 +5111,44 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>3044747</v>
+        <v>-159478</v>
       </c>
       <c r="C40">
-        <v>9875175</v>
-      </c>
-      <c r="D40">
-        <v>11078107</v>
+        <v>-16242130</v>
+      </c>
+      <c r="E40">
+        <v>-587350</v>
       </c>
       <c r="F40">
-        <v>2178340</v>
-      </c>
-      <c r="G40">
-        <v>-8448033</v>
+        <v>-9411702</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B41">
+        <v>-8197</v>
+      </c>
+      <c r="E41">
+        <v>-88491</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>245931</v>
+        <v>1924257</v>
       </c>
       <c r="C42">
-        <v>-4287332</v>
-      </c>
-      <c r="D42">
-        <v>658208</v>
+        <v>-926411</v>
+      </c>
+      <c r="E42">
+        <v>584100</v>
       </c>
       <c r="F42">
-        <v>829207</v>
-      </c>
-      <c r="G42">
-        <v>-476087</v>
+        <v>-5459674</v>
       </c>
     </row>
     <row r="43">
@@ -5372,19 +5161,16 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-17433310</v>
+        <v>-5787820</v>
       </c>
       <c r="C44">
-        <v>-15032357</v>
-      </c>
-      <c r="D44">
-        <v>-498360</v>
+        <v>-13730059</v>
+      </c>
+      <c r="E44">
+        <v>-5207717</v>
       </c>
       <c r="F44">
-        <v>27661255</v>
-      </c>
-      <c r="G44">
-        <v>1887</v>
+        <v>-11329106</v>
       </c>
     </row>
     <row r="45">
@@ -5401,31 +5187,22 @@
       <c r="A47" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
-      <c r="F47">
-        <v>-184625</v>
-      </c>
-      <c r="G47">
-        <v>-285236</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>-290</v>
       </c>
       <c r="C48">
-        <v>-6632796</v>
-      </c>
-      <c r="D48">
-        <v>-6234658</v>
+        <v>243235</v>
+      </c>
+      <c r="E48">
+        <v>-4316941</v>
       </c>
       <c r="F48">
-        <v>-874625</v>
-      </c>
-      <c r="G48">
-        <v>1042626</v>
+        <v>-6389561</v>
       </c>
     </row>
     <row r="49">
@@ -5433,7 +5210,10 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>286120396</v>
+        <v>13074643</v>
+      </c>
+      <c r="E49">
+        <v>49767187</v>
       </c>
     </row>
     <row r="50">
@@ -5522,19 +5302,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-49204258</v>
+        <v>-533599839</v>
       </c>
       <c r="C67">
-        <v>-46885999</v>
-      </c>
-      <c r="D67">
-        <v>-4865360</v>
+        <v>-5518304</v>
+      </c>
+      <c r="E67">
+        <v>-16659266</v>
       </c>
       <c r="F67">
-        <v>109763</v>
-      </c>
-      <c r="G67">
-        <v>-163903</v>
+        <v>-3200045</v>
       </c>
     </row>
     <row r="68">
@@ -5581,6 +5358,9 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="B76">
+        <v>-533378718</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -5592,19 +5372,16 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-49204258</v>
+        <v>-221121</v>
       </c>
       <c r="C78">
-        <v>-199585377</v>
-      </c>
-      <c r="D78">
-        <v>-157564738</v>
+        <v>-5518304</v>
+      </c>
+      <c r="E78">
+        <v>-16659266</v>
       </c>
       <c r="F78">
-        <v>-5872001</v>
-      </c>
-      <c r="G78">
-        <v>-5972118</v>
+        <v>-155899423</v>
       </c>
     </row>
     <row r="79">
@@ -5718,19 +5495,16 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-164631344</v>
+        <v>500126481</v>
       </c>
       <c r="C101">
-        <v>-368545601</v>
-      </c>
-      <c r="D101">
-        <v>-230184273</v>
+        <v>-73477495</v>
+      </c>
+      <c r="E101">
+        <v>-22715601</v>
       </c>
       <c r="F101">
-        <v>-168788616</v>
-      </c>
-      <c r="G101">
-        <v>-140483941</v>
+        <v>-277391752</v>
       </c>
     </row>
     <row r="102">
@@ -5748,7 +5522,7 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>544447675</v>
       </c>
     </row>
     <row r="105">
@@ -5765,9 +5539,6 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="F107">
-        <v>18816970</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5779,13 +5550,16 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>125000000</v>
+        <v>50000000</v>
       </c>
       <c r="C109">
-        <v>63048804</v>
-      </c>
-      <c r="D109">
-        <v>10000000</v>
+        <v>65000000</v>
+      </c>
+      <c r="E109">
+        <v>50000000</v>
+      </c>
+      <c r="F109">
+        <v>3048804</v>
       </c>
     </row>
     <row r="110">
@@ -5793,19 +5567,16 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-237870260</v>
+        <v>-77526539</v>
       </c>
       <c r="C110">
-        <v>-296256903</v>
-      </c>
-      <c r="D110">
-        <v>-198202238</v>
+        <v>-52960658</v>
+      </c>
+      <c r="E110">
+        <v>-53450798</v>
       </c>
       <c r="F110">
-        <v>-144449911</v>
-      </c>
-      <c r="G110">
-        <v>-99622084</v>
+        <v>-111347301</v>
       </c>
     </row>
     <row r="111">
@@ -5823,7 +5594,10 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-3247231</v>
+        <v>-2293451</v>
+      </c>
+      <c r="E113">
+        <v>3648569</v>
       </c>
     </row>
     <row r="114">
@@ -5851,19 +5625,16 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-50405861</v>
+        <v>-15042330</v>
       </c>
       <c r="C118">
-        <v>-59887377</v>
-      </c>
-      <c r="D118">
-        <v>-52512446</v>
+        <v>-85729508</v>
+      </c>
+      <c r="E118">
+        <v>-23156366</v>
       </c>
       <c r="F118">
-        <v>-56322474</v>
-      </c>
-      <c r="G118">
-        <v>-42972564</v>
+        <v>-95211024</v>
       </c>
     </row>
     <row r="119">
@@ -5871,19 +5642,16 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>1892008</v>
+        <v>541126</v>
       </c>
       <c r="C119">
-        <v>7618495</v>
-      </c>
-      <c r="D119">
-        <v>5074031</v>
+        <v>3459902</v>
+      </c>
+      <c r="E119">
+        <v>242994</v>
       </c>
       <c r="F119">
-        <v>1686799</v>
-      </c>
-      <c r="G119">
-        <v>965385</v>
+        <v>9186389</v>
       </c>
     </row>
     <row r="120">
@@ -5916,7 +5684,10 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>72284794</v>
+        <v>-20398715</v>
+      </c>
+      <c r="E125">
+        <v>10392320</v>
       </c>
     </row>
     <row r="126">
@@ -5924,7 +5695,13 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-14752202</v>
+        <v>-1690097</v>
+      </c>
+      <c r="C126">
+        <v>-82253969</v>
+      </c>
+      <c r="E126">
+        <v>-1425070</v>
       </c>
     </row>
     <row r="127">
@@ -5932,19 +5709,16 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>57532592</v>
+        <v>-22088812</v>
       </c>
       <c r="C127">
-        <v>-11542599</v>
-      </c>
-      <c r="D127">
-        <v>-11056373</v>
+        <v>60156532</v>
+      </c>
+      <c r="E127">
+        <v>8967250</v>
       </c>
       <c r="F127">
-        <v>12267042</v>
-      </c>
-      <c r="G127">
-        <v>-1544385</v>
+        <v>-8918659</v>
       </c>
     </row>
     <row r="128">
@@ -5952,6 +5726,9 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
+        <v>68795052</v>
+      </c>
+      <c r="E128">
         <v>11262460</v>
       </c>
     </row>
@@ -5960,12 +5737,1178 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>68795052</v>
+        <v>46706240</v>
+      </c>
+      <c r="E129">
+        <v>20229710</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I129"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
+    <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Kalem</v>
+      </c>
+      <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="F1" t="str">
+        <v>2024/12</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2023/12</v>
+      </c>
+      <c r="I1" t="str">
+        <v>2022/12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B3">
+        <v>249427852</v>
+      </c>
+      <c r="C3">
+        <v>286120396</v>
+      </c>
+      <c r="D3">
+        <v>829015291</v>
+      </c>
+      <c r="F3">
+        <v>376692638</v>
+      </c>
+      <c r="H3">
+        <v>186927659</v>
+      </c>
+      <c r="I3">
+        <v>144911674</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
+      </c>
+      <c r="B4">
+        <v>113141811</v>
+      </c>
+      <c r="C4">
+        <v>190257696</v>
+      </c>
+      <c r="D4">
+        <v>220069775</v>
+      </c>
+      <c r="F4">
+        <v>122002089</v>
+      </c>
+      <c r="H4">
+        <v>52909752</v>
+      </c>
+      <c r="I4">
+        <v>69696677</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B5">
+        <v>128159374</v>
+      </c>
+      <c r="C5">
+        <v>127844046</v>
+      </c>
+      <c r="D5">
+        <v>636202770</v>
+      </c>
+      <c r="F5">
+        <v>250373687</v>
+      </c>
+      <c r="H5">
+        <v>136533277</v>
+      </c>
+      <c r="I5">
+        <v>70647067</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B6">
+        <v>163156473</v>
+      </c>
+      <c r="C6">
+        <v>155543420</v>
+      </c>
+      <c r="D6">
+        <v>269394939</v>
+      </c>
+      <c r="F6">
+        <v>237253862</v>
+      </c>
+      <c r="H6">
+        <v>84819402</v>
+      </c>
+      <c r="I6">
+        <v>55472384</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B8">
+        <v>1420852</v>
+      </c>
+      <c r="C8">
+        <v>1997373</v>
+      </c>
+      <c r="D8">
+        <v>2603489</v>
+      </c>
+      <c r="F8">
+        <v>1085016</v>
+      </c>
+      <c r="H8">
+        <v>302668</v>
+      </c>
+      <c r="I8">
+        <v>121363</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B12">
+        <v>123705307</v>
+      </c>
+      <c r="C12">
+        <v>132536873</v>
+      </c>
+      <c r="D12">
+        <v>-80749912</v>
+      </c>
+      <c r="F12">
+        <v>-5272151</v>
+      </c>
+      <c r="H12">
+        <v>-2054919</v>
+      </c>
+      <c r="I12">
+        <v>-1530385</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="C15">
+        <v>-350298446</v>
+      </c>
+      <c r="D15">
+        <v>-53697792</v>
+      </c>
+      <c r="F15">
+        <v>-53370186</v>
+      </c>
+      <c r="H15">
+        <v>-3495728</v>
+      </c>
+      <c r="I15">
+        <v>-40750112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B20">
+        <v>164517060</v>
+      </c>
+      <c r="C20">
+        <v>188064826</v>
+      </c>
+      <c r="D20">
+        <v>-73669177</v>
+      </c>
+      <c r="F20">
+        <v>-17385849</v>
+      </c>
+      <c r="H20">
+        <v>-14976707</v>
+      </c>
+      <c r="I20">
+        <v>-358113</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="I22">
+        <v>-635973</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
+      </c>
+      <c r="B28">
+        <v>8126667</v>
+      </c>
+      <c r="C28">
+        <v>-31981346</v>
+      </c>
+      <c r="D28">
+        <v>-27257254</v>
+      </c>
+      <c r="F28">
+        <v>4316862</v>
+      </c>
+      <c r="H28">
+        <v>-2515370</v>
+      </c>
+      <c r="I28">
+        <v>4567930</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
+      </c>
+      <c r="C29">
+        <v>-580444</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabındaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B31">
+        <v>19005426</v>
+      </c>
+      <c r="C31">
+        <v>-17667689</v>
+      </c>
+      <c r="D31">
+        <v>-6657084</v>
+      </c>
+      <c r="F31">
+        <v>5792801</v>
+      </c>
+      <c r="H31">
+        <v>-3795052</v>
+      </c>
+      <c r="I31">
+        <v>-1991389</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B33">
+        <v>-750767</v>
+      </c>
+      <c r="C33">
+        <v>558666</v>
+      </c>
+      <c r="D33">
+        <v>9381498</v>
+      </c>
+      <c r="F33">
+        <v>8017380</v>
+      </c>
+      <c r="H33">
+        <v>7520321</v>
+      </c>
+      <c r="I33">
+        <v>6327903</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">    Canlı Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
+      </c>
+      <c r="B39">
+        <v>-989787</v>
+      </c>
+      <c r="C39">
+        <v>-149247</v>
+      </c>
+      <c r="D39">
+        <v>309187</v>
+      </c>
+      <c r="F39">
+        <v>173131</v>
+      </c>
+      <c r="H39">
+        <v>-391821</v>
+      </c>
+      <c r="I39">
+        <v>-2059531</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B40">
+        <v>3472619</v>
+      </c>
+      <c r="C40">
+        <v>3044747</v>
+      </c>
+      <c r="D40">
+        <v>9875175</v>
+      </c>
+      <c r="F40">
+        <v>11078107</v>
+      </c>
+      <c r="H40">
+        <v>2178340</v>
+      </c>
+      <c r="I40">
+        <v>-8448033</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
+      </c>
+      <c r="B42">
+        <v>1586088</v>
+      </c>
+      <c r="C42">
+        <v>245931</v>
+      </c>
+      <c r="D42">
+        <v>-4287332</v>
+      </c>
+      <c r="F42">
+        <v>658208</v>
+      </c>
+      <c r="H42">
+        <v>829207</v>
+      </c>
+      <c r="I42">
+        <v>-476087</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B44">
+        <v>-18013413</v>
+      </c>
+      <c r="C44">
+        <v>-17433310</v>
+      </c>
+      <c r="D44">
+        <v>-15032357</v>
+      </c>
+      <c r="F44">
+        <v>-498360</v>
+      </c>
+      <c r="H44">
+        <v>27661255</v>
+      </c>
+      <c r="I44">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Türev Yükümlülüklerdeki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımlarındaki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
+      </c>
+      <c r="H47">
+        <v>-184625</v>
+      </c>
+      <c r="I47">
+        <v>-285236</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B48">
+        <v>4316651</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>-6632796</v>
+      </c>
+      <c r="F48">
+        <v>-6234658</v>
+      </c>
+      <c r="H48">
+        <v>-874625</v>
+      </c>
+      <c r="I48">
+        <v>1042626</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
+      </c>
+      <c r="B49">
+        <v>249427852</v>
+      </c>
+      <c r="C49">
+        <v>286120396</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Kira Ödemeleri</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Alınan Kira</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-566144831</v>
+      </c>
+      <c r="C67">
+        <v>-49204258</v>
+      </c>
+      <c r="D67">
+        <v>-46885999</v>
+      </c>
+      <c r="F67">
+        <v>-4865360</v>
+      </c>
+      <c r="H67">
+        <v>109763</v>
+      </c>
+      <c r="I67">
+        <v>-163903</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-32766113</v>
+      </c>
+      <c r="C78">
+        <v>-49204258</v>
+      </c>
+      <c r="D78">
+        <v>-199585377</v>
+      </c>
+      <c r="F78">
+        <v>-157564738</v>
+      </c>
+      <c r="H78">
+        <v>-5872001</v>
+      </c>
+      <c r="I78">
+        <v>-5972118</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>358210738</v>
+      </c>
+      <c r="C101">
+        <v>-164631344</v>
+      </c>
+      <c r="D101">
+        <v>-368545601</v>
+      </c>
+      <c r="F101">
+        <v>-230184273</v>
+      </c>
+      <c r="H101">
+        <v>-168788616</v>
+      </c>
+      <c r="I101">
+        <v>-140483941</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="H107">
+        <v>18816970</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B109">
+        <v>125000000</v>
+      </c>
+      <c r="C109">
+        <v>125000000</v>
+      </c>
+      <c r="D109">
+        <v>63048804</v>
+      </c>
+      <c r="F109">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-261946001</v>
+      </c>
+      <c r="C110">
+        <v>-237870260</v>
+      </c>
+      <c r="D110">
+        <v>-296256903</v>
+      </c>
+      <c r="F110">
+        <v>-198202238</v>
+      </c>
+      <c r="H110">
+        <v>-144449911</v>
+      </c>
+      <c r="I110">
+        <v>-99622084</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B113">
+        <v>-9189251</v>
+      </c>
+      <c r="C113">
+        <v>-3247231</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-42291825</v>
+      </c>
+      <c r="C118">
+        <v>-50405861</v>
+      </c>
+      <c r="D118">
+        <v>-59887377</v>
+      </c>
+      <c r="F118">
+        <v>-52512446</v>
+      </c>
+      <c r="H118">
+        <v>-56322474</v>
+      </c>
+      <c r="I118">
+        <v>-42972564</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="B119">
+        <v>2190140</v>
+      </c>
+      <c r="C119">
+        <v>1892008</v>
+      </c>
+      <c r="D119">
+        <v>7618495</v>
+      </c>
+      <c r="F119">
+        <v>5074031</v>
+      </c>
+      <c r="H119">
+        <v>1686799</v>
+      </c>
+      <c r="I119">
+        <v>965385</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>41493759</v>
+      </c>
+      <c r="C125">
+        <v>72284794</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+      </c>
+      <c r="B126">
+        <v>-15017229</v>
+      </c>
+      <c r="C126">
+        <v>-14752202</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>26476530</v>
+      </c>
+      <c r="C127">
+        <v>57532592</v>
+      </c>
+      <c r="D127">
+        <v>-11542599</v>
+      </c>
+      <c r="F127">
+        <v>-11056373</v>
+      </c>
+      <c r="H127">
+        <v>12267042</v>
+      </c>
+      <c r="I127">
+        <v>-1544385</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B128">
+        <v>68795052</v>
+      </c>
+      <c r="C128">
+        <v>11262460</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>95271582</v>
+      </c>
+      <c r="C129">
+        <v>68795052</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/BESTE (TRY).xlsx
+++ b/data/BESTE (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,21 +451,24 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
+        <v>53329283</v>
+      </c>
+      <c r="C3">
         <v>46706240</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>68795052</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>8638520</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>11262460</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>22318833</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>10051791</v>
       </c>
     </row>
@@ -475,6 +482,9 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
+        <v>480158053</v>
+      </c>
+      <c r="C5">
         <v>533378718</v>
       </c>
     </row>
@@ -488,21 +498,24 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
+        <v>66351297</v>
+      </c>
+      <c r="C7">
         <v>39167605</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>51594687</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>82188321</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>33806359</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>37220175</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>24357849</v>
       </c>
     </row>
@@ -521,18 +534,21 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
+        <v>71119917</v>
+      </c>
+      <c r="C10">
         <v>708445</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>708640</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>1207997</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>239795</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>5224402</v>
       </c>
     </row>
@@ -571,21 +587,21 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
+        <v>2909464</v>
+      </c>
+      <c r="C17">
         <v>1993432</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
+      <c r="E17">
         <v>853878</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>223324</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>99647</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>368675</v>
       </c>
     </row>
@@ -598,6 +614,12 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
+      <c r="B19">
+        <v>755708</v>
+      </c>
+      <c r="D19">
+        <v>543629</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -609,21 +631,21 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
+        <v>7810</v>
+      </c>
+      <c r="C21">
         <v>552116</v>
       </c>
-      <c r="C21">
-        <v>543629</v>
-      </c>
-      <c r="D21">
+      <c r="E21">
         <v>486916</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>243681</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>1889275</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>1802218</v>
       </c>
     </row>
@@ -642,21 +664,24 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
+        <v>674631532</v>
+      </c>
+      <c r="C24">
         <v>622506556</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>121642008</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>92167635</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>46743821</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>61767725</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>41804935</v>
       </c>
     </row>
@@ -693,18 +718,21 @@
         <v>357891</v>
       </c>
       <c r="C30">
+        <v>357891</v>
+      </c>
+      <c r="D30">
         <v>324117</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>403114</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>383426</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>312873</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1976</v>
       </c>
     </row>
@@ -742,7 +770,7 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>50405973</v>
       </c>
     </row>
@@ -756,21 +784,24 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
+        <v>4990529179</v>
+      </c>
+      <c r="C39">
         <v>4790833692</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>4663238585</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>4536412943</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>3925991360</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>2738078086</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>1785693132</v>
       </c>
     </row>
@@ -779,21 +810,24 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
+        <v>8963441</v>
+      </c>
+      <c r="C40">
         <v>9815489</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>6114681</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>6483196</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>7865919</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>3208450</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>1163983</v>
       </c>
     </row>
@@ -802,9 +836,12 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
+        <v>3473388</v>
+      </c>
+      <c r="C41">
         <v>3445347</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>3562306</v>
       </c>
     </row>
@@ -813,21 +850,24 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
+        <v>623835</v>
+      </c>
+      <c r="C42">
         <v>5524</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>1920600</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>1330705</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>1548019</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>1844837</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>1183988</v>
       </c>
     </row>
@@ -856,21 +896,24 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
+        <v>5003947734</v>
+      </c>
+      <c r="C47">
         <v>4804457943</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>4675160289</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>4544629958</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>3935788734</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>2743444246</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>1838449052</v>
       </c>
     </row>
@@ -879,21 +922,24 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
+        <v>5678579266</v>
+      </c>
+      <c r="C48">
         <v>5426964499</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>4796802297</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>4636797593</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>3982532555</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>2805211971</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>1880253987</v>
       </c>
     </row>
@@ -907,21 +953,24 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
+        <v>178935332</v>
+      </c>
+      <c r="C50">
         <v>181274705</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>221207880</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>152649712</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>166810514</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>213162125</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>144362439</v>
       </c>
     </row>
@@ -935,21 +984,24 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
+        <v>35048334</v>
+      </c>
+      <c r="C52">
         <v>17777251</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>17894916</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>33656896</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>14370019</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>4009125</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>1830785</v>
       </c>
     </row>
@@ -963,21 +1015,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
+        <v>2307612</v>
+      </c>
+      <c r="C54">
         <v>2548393</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>624136</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>1610122</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>378205</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>1036413</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>330515</v>
       </c>
     </row>
@@ -986,21 +1041,24 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
+        <v>15175127</v>
+      </c>
+      <c r="C55">
         <v>19246970</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>25034790</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>41375272</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>45078523</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>45576883</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>42137918</v>
       </c>
     </row>
@@ -1028,7 +1086,7 @@
       <c r="A60" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>184625</v>
       </c>
     </row>
@@ -1042,21 +1100,24 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
+        <v>1337296</v>
+      </c>
+      <c r="C62">
         <v>828928</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>741021</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>1320923</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>1031384</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>1041514</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>550085</v>
       </c>
     </row>
@@ -1080,21 +1141,24 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
+        <v>232803701</v>
+      </c>
+      <c r="C66">
         <v>221676247</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>265502743</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>230612925</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>227668645</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>264826060</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>189396367</v>
       </c>
     </row>
@@ -1108,21 +1172,24 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
+        <v>74969860</v>
+      </c>
+      <c r="C68">
         <v>105220983</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>117913883</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>139709436</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>200005538</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>263401307</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>297187769</v>
       </c>
     </row>
@@ -1186,21 +1253,24 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
+        <v>1572675</v>
+      </c>
+      <c r="C80">
         <v>1741373</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>2348569</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>2698854</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>855688</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>420419</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>242882</v>
       </c>
     </row>
@@ -1214,21 +1284,24 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
+        <v>349768001</v>
+      </c>
+      <c r="C82">
         <v>760695156</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>770576622</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>707770061</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>582511798</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>351135952</v>
       </c>
-      <c r="G82">
+      <c r="H82">
         <v>235040755</v>
       </c>
     </row>
@@ -1242,21 +1315,24 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
+        <v>426310536</v>
+      </c>
+      <c r="C84">
         <v>867657512</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>890839074</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>850178351</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>783373024</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>614957678</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>532471406</v>
       </c>
     </row>
@@ -1270,21 +1346,24 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
+        <v>5019465029</v>
+      </c>
+      <c r="C86">
         <v>4337630740</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>3640460480</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>3556006317</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>2971490886</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>1925428233</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>1159866961</v>
       </c>
     </row>
@@ -1296,7 +1375,7 @@
         <v>188205000</v>
       </c>
       <c r="C87">
-        <v>150000000</v>
+        <v>188205000</v>
       </c>
       <c r="D87">
         <v>150000000</v>
@@ -1305,9 +1384,12 @@
         <v>150000000</v>
       </c>
       <c r="F87">
+        <v>150000000</v>
+      </c>
+      <c r="G87">
         <v>61475000</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>50000000</v>
       </c>
     </row>
@@ -1348,6 +1430,9 @@
       <c r="B94">
         <v>506242675</v>
       </c>
+      <c r="C94">
+        <v>506242675</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -1364,12 +1449,15 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
+        <v>3262630525</v>
+      </c>
+      <c r="C97">
         <v>666774209</v>
       </c>
-      <c r="C97">
-        <v>665226146</v>
-      </c>
       <c r="D97">
+        <v>2719129454</v>
+      </c>
+      <c r="E97">
         <v>665468811</v>
       </c>
     </row>
@@ -1377,11 +1465,8 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
-      <c r="B98">
+      <c r="C98">
         <v>2245908680</v>
-      </c>
-      <c r="C98">
-        <v>2053903308</v>
       </c>
     </row>
     <row r="99">
@@ -1393,16 +1478,16 @@
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>1980629349</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>2240417556</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>1316356992</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>596363502</v>
       </c>
     </row>
@@ -1424,18 +1509,21 @@
         <v>771331026</v>
       </c>
       <c r="C103">
-        <v>581073330</v>
+        <v>771331026</v>
       </c>
       <c r="D103">
         <v>581073330</v>
       </c>
       <c r="E103">
+        <v>581073330</v>
+      </c>
+      <c r="F103">
         <v>459071241</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>494686489</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>443806782</v>
       </c>
     </row>
@@ -1444,21 +1532,24 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
+        <v>291055803</v>
+      </c>
+      <c r="C104">
         <v>-40830850</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>190257696</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>178834827</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>122002089</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>52909752</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>69696677</v>
       </c>
     </row>
@@ -1472,21 +1563,24 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
+        <v>5019465029</v>
+      </c>
+      <c r="C106">
         <v>4337630740</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>3640460480</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>3556006317</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>2971490886</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>1925428233</v>
       </c>
-      <c r="G106">
+      <c r="H106">
         <v>1158386214</v>
       </c>
     </row>
@@ -1495,21 +1589,24 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
+        <v>5678579266</v>
+      </c>
+      <c r="C107">
         <v>5426964499</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>4796802297</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>4636797593</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>3982532555</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>2805211971</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>1880253987</v>
       </c>
     </row>
@@ -1517,17 +1614,23 @@
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B108">
+        <v>26443587</v>
+      </c>
+      <c r="C108">
+        <v>-272109090</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1538,6 +1641,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1545,27 +1650,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1579,27 +1690,33 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>168088900</v>
+      </c>
+      <c r="C3">
         <v>51818936</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>448686813</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>346581538</v>
       </c>
-      <c r="E3">
-        <v>67266312</v>
-      </c>
       <c r="F3">
+        <v>201463117</v>
+      </c>
+      <c r="G3">
+        <v>84262514</v>
+      </c>
+      <c r="H3">
         <v>345482207</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>265504087</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>287515179</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>178947454</v>
       </c>
     </row>
@@ -1623,27 +1740,33 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-173351483</v>
+      </c>
+      <c r="C7">
         <v>-76560889</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-323651484</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-246495873</v>
       </c>
-      <c r="E7">
+      <c r="F7">
+        <v>-126237817</v>
+      </c>
+      <c r="G7">
         <v>-59848344</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-257480356</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>-149830831</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-188330683</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-81596607</v>
       </c>
     </row>
@@ -1652,27 +1775,33 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>-5262583</v>
+      </c>
+      <c r="C8">
         <v>-24741953</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>125035329</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>100085665</v>
       </c>
-      <c r="E8">
-        <v>7417968</v>
-      </c>
       <c r="F8">
+        <v>75225300</v>
+      </c>
+      <c r="G8">
+        <v>24414170</v>
+      </c>
+      <c r="H8">
         <v>88001851</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>115673256</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>99184496</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>97350847</v>
       </c>
     </row>
@@ -1680,34 +1809,16 @@
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1719,27 +1830,33 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>-5262583</v>
+      </c>
+      <c r="C13">
         <v>-24741953</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>125035329</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>100085665</v>
       </c>
-      <c r="E13">
-        <v>7417968</v>
-      </c>
       <c r="F13">
+        <v>75225300</v>
+      </c>
+      <c r="G13">
+        <v>24414170</v>
+      </c>
+      <c r="H13">
         <v>88001851</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>115673256</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>99184496</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>97350847</v>
       </c>
     </row>
@@ -1749,27 +1866,33 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-23130813</v>
+        <v>-23349367</v>
       </c>
       <c r="C15">
+        <v>-14213181</v>
+      </c>
+      <c r="D15">
         <v>-18658866</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-12695234</v>
       </c>
-      <c r="E15">
+      <c r="F15">
+        <v>-18471567</v>
+      </c>
+      <c r="G15">
         <v>-2770069</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-25065759</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-6792315</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-15872106</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-10691285</v>
       </c>
     </row>
@@ -1777,6 +1900,18 @@
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
+      <c r="B16">
+        <v>-9169661</v>
+      </c>
+      <c r="C16">
+        <v>-8917632</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1788,27 +1923,33 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>1365434</v>
+      </c>
+      <c r="C18">
         <v>412034</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>2679624</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>2764396</v>
       </c>
-      <c r="E18">
-        <v>17303662</v>
-      </c>
       <c r="F18">
+        <v>2699027</v>
+      </c>
+      <c r="G18">
+        <v>307460</v>
+      </c>
+      <c r="H18">
         <v>2622648</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>4344339</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>6058934</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>10801617</v>
       </c>
     </row>
@@ -1817,27 +1958,33 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-6639491</v>
+      </c>
+      <c r="C19">
         <v>-3598962</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-15373582</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-17020945</v>
       </c>
-      <c r="E19">
+      <c r="F19">
+        <v>-2147551</v>
+      </c>
+      <c r="G19">
         <v>-973496</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>-2840412</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>-8985861</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>-878099</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-4621841</v>
       </c>
     </row>
@@ -1851,27 +1998,33 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-43055668</v>
+      </c>
+      <c r="C21">
         <v>-51059694</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>93682505</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>73133882</v>
       </c>
-      <c r="E21">
+      <c r="F21">
+        <v>57305209</v>
+      </c>
+      <c r="G21">
         <v>20978065</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>62718328</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>104239419</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>88493225</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>92839338</v>
       </c>
     </row>
@@ -1891,12 +2044,21 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>75613499</v>
+      </c>
+      <c r="C25">
         <v>25647509</v>
       </c>
-      <c r="H25">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>1281157</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>6272173</v>
       </c>
     </row>
@@ -1904,7 +2066,7 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>-19680306</v>
       </c>
     </row>
@@ -1943,27 +2105,33 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>32557831</v>
+      </c>
+      <c r="C33">
         <v>-25412185</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>93682505</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>73133882</v>
       </c>
-      <c r="E33">
+      <c r="F33">
+        <v>57305209</v>
+      </c>
+      <c r="G33">
         <v>20978065</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>62718328</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>104239419</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>70094076</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>99111511</v>
       </c>
     </row>
@@ -1973,27 +2141,33 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>23407918</v>
+      </c>
+      <c r="C35">
         <v>5612971</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>226241670</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>163265404</v>
       </c>
-      <c r="E35">
+      <c r="F35">
+        <v>141719761</v>
+      </c>
+      <c r="G35">
         <v>54248589</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>129246505</v>
       </c>
-      <c r="G35">
+      <c r="I35">
         <v>39608134</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>213370889</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>161654973</v>
       </c>
     </row>
@@ -2002,27 +2176,33 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-116467886</v>
+      </c>
+      <c r="C36">
         <v>-58577736</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-72684977</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-37857848</v>
       </c>
-      <c r="E36">
+      <c r="F36">
+        <v>-54396405</v>
+      </c>
+      <c r="G36">
         <v>-52909462</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-87348593</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>-61998142</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-245531920</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-191427919</v>
       </c>
     </row>
@@ -2031,7 +2211,16 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
+        <v>73152</v>
+      </c>
+      <c r="C37">
         <v>30491</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2039,27 +2228,33 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>-60428985</v>
+      </c>
+      <c r="C38">
         <v>-78346459</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>247239198</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>198541438</v>
       </c>
-      <c r="E38">
+      <c r="F38">
+        <v>144628565</v>
+      </c>
+      <c r="G38">
         <v>22317192</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>104616240</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>81849411</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>37933045</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>69338565</v>
       </c>
     </row>
@@ -2069,21 +2264,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>351484788</v>
+      </c>
+      <c r="C40">
         <v>37515609</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-56981502</v>
       </c>
-      <c r="E40">
+      <c r="F40">
+        <v>3696610</v>
+      </c>
+      <c r="G40">
         <v>13967843</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>17385849</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>14976707</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>358113</v>
       </c>
     </row>
@@ -2091,7 +2292,7 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>-33</v>
       </c>
     </row>
@@ -2100,27 +2301,33 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>351484788</v>
+      </c>
+      <c r="C42">
         <v>37515609</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-56981502</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>-19706611</v>
       </c>
-      <c r="E42">
+      <c r="F42">
+        <v>3696610</v>
+      </c>
+      <c r="G42">
         <v>13967843</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>17385849</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>-1082270</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>14976707</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>358080</v>
       </c>
     </row>
@@ -2129,27 +2336,33 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>291055803</v>
+      </c>
+      <c r="C43">
         <v>-40830850</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>190257696</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>198541438</v>
       </c>
-      <c r="E43">
+      <c r="F43">
+        <v>148325175</v>
+      </c>
+      <c r="G43">
         <v>36285035</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>122002089</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>81849411</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>52909752</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>69696678</v>
       </c>
     </row>
@@ -2164,27 +2377,33 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>291055803</v>
+      </c>
+      <c r="C46">
         <v>-40830850</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>190257696</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>178834827</v>
       </c>
-      <c r="E46">
+      <c r="F46">
+        <v>148325175</v>
+      </c>
+      <c r="G46">
         <v>36285035</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>122002089</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>80767141</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>52909752</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>69696678</v>
       </c>
     </row>
@@ -2198,7 +2417,13 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2207,27 +2432,33 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>291055803</v>
+      </c>
+      <c r="C48">
         <v>-40830850</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>190257696</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>178834827</v>
       </c>
-      <c r="E48">
+      <c r="F48">
+        <v>148325175</v>
+      </c>
+      <c r="G48">
         <v>36285035</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>122002089</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>80767141</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>52909752</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>69696678</v>
       </c>
     </row>
@@ -2237,40 +2468,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>86602380</v>
+      </c>
+      <c r="C50">
         <v>42110846</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>155543420</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>111727030</v>
       </c>
-      <c r="E50">
+      <c r="F50">
+        <v>71003787</v>
+      </c>
+      <c r="G50">
         <v>34497793</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>237253862</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>79585953</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>84819402</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>55472384</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2281,6 +2518,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2288,27 +2527,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2322,15 +2567,24 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>116269964</v>
+      </c>
+      <c r="C3">
         <v>51818936</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>102105275</v>
       </c>
       <c r="E3">
-        <v>67266312</v>
+        <v>145118421</v>
       </c>
       <c r="F3">
+        <v>117200603</v>
+      </c>
+      <c r="G3">
+        <v>84262514</v>
+      </c>
+      <c r="H3">
         <v>79978120</v>
       </c>
     </row>
@@ -2354,15 +2608,24 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-96790594</v>
+      </c>
+      <c r="C7">
         <v>-76560889</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-77155611</v>
       </c>
       <c r="E7">
+        <v>-120258056</v>
+      </c>
+      <c r="F7">
+        <v>-66389473</v>
+      </c>
+      <c r="G7">
         <v>-59848344</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-107649525</v>
       </c>
     </row>
@@ -2371,15 +2634,24 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>19479370</v>
+      </c>
+      <c r="C8">
         <v>-24741953</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>24949664</v>
       </c>
       <c r="E8">
-        <v>7417968</v>
+        <v>24860365</v>
       </c>
       <c r="F8">
+        <v>50811130</v>
+      </c>
+      <c r="G8">
+        <v>24414170</v>
+      </c>
+      <c r="H8">
         <v>-27671405</v>
       </c>
     </row>
@@ -2387,34 +2659,16 @@
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2426,15 +2680,24 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>19479370</v>
+      </c>
+      <c r="C13">
         <v>-24741953</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>24949664</v>
       </c>
       <c r="E13">
-        <v>7417968</v>
+        <v>24860365</v>
       </c>
       <c r="F13">
+        <v>50811130</v>
+      </c>
+      <c r="G13">
+        <v>24414170</v>
+      </c>
+      <c r="H13">
         <v>-27671405</v>
       </c>
     </row>
@@ -2444,15 +2707,24 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-23130813</v>
+        <v>-9136186</v>
       </c>
       <c r="C15">
+        <v>-14213181</v>
+      </c>
+      <c r="D15">
         <v>-5963632</v>
       </c>
       <c r="E15">
+        <v>5776333</v>
+      </c>
+      <c r="F15">
+        <v>-15701498</v>
+      </c>
+      <c r="G15">
         <v>-2770069</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-18273444</v>
       </c>
     </row>
@@ -2460,6 +2732,18 @@
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
+      <c r="B16">
+        <v>-252029</v>
+      </c>
+      <c r="C16">
+        <v>-8917632</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -2471,15 +2755,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>953400</v>
+      </c>
+      <c r="C18">
         <v>412034</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-84772</v>
       </c>
       <c r="E18">
-        <v>17303662</v>
+        <v>65369</v>
       </c>
       <c r="F18">
+        <v>2391567</v>
+      </c>
+      <c r="G18">
+        <v>307460</v>
+      </c>
+      <c r="H18">
         <v>-1721691</v>
       </c>
     </row>
@@ -2488,15 +2781,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-3040529</v>
+      </c>
+      <c r="C19">
         <v>-3598962</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>1647363</v>
       </c>
       <c r="E19">
+        <v>-14873394</v>
+      </c>
+      <c r="F19">
+        <v>-1174055</v>
+      </c>
+      <c r="G19">
         <v>-973496</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>6145449</v>
       </c>
     </row>
@@ -2510,15 +2812,24 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>8004026</v>
+      </c>
+      <c r="C21">
         <v>-51059694</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>20548623</v>
       </c>
       <c r="E21">
+        <v>15828673</v>
+      </c>
+      <c r="F21">
+        <v>36327144</v>
+      </c>
+      <c r="G21">
         <v>20978065</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>-41521091</v>
       </c>
     </row>
@@ -2538,7 +2849,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>49965990</v>
+      </c>
+      <c r="C25">
         <v>25647509</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2581,15 +2901,24 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>57970016</v>
+      </c>
+      <c r="C33">
         <v>-25412185</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>20548623</v>
       </c>
       <c r="E33">
+        <v>15828673</v>
+      </c>
+      <c r="F33">
+        <v>36327144</v>
+      </c>
+      <c r="G33">
         <v>20978065</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>-41521091</v>
       </c>
     </row>
@@ -2599,15 +2928,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>17794947</v>
+      </c>
+      <c r="C35">
         <v>5612971</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>62976266</v>
       </c>
       <c r="E35">
+        <v>21545643</v>
+      </c>
+      <c r="F35">
+        <v>87471172</v>
+      </c>
+      <c r="G35">
         <v>54248589</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>89638371</v>
       </c>
     </row>
@@ -2616,15 +2954,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-57890150</v>
+      </c>
+      <c r="C36">
         <v>-58577736</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-34827129</v>
       </c>
       <c r="E36">
+        <v>16538557</v>
+      </c>
+      <c r="F36">
+        <v>-1486943</v>
+      </c>
+      <c r="G36">
         <v>-52909462</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-25350451</v>
       </c>
     </row>
@@ -2633,7 +2980,16 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
+        <v>42661</v>
+      </c>
+      <c r="C37">
         <v>30491</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2641,15 +2997,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>17917474</v>
+      </c>
+      <c r="C38">
         <v>-78346459</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>48697760</v>
       </c>
       <c r="E38">
+        <v>53912873</v>
+      </c>
+      <c r="F38">
+        <v>122311373</v>
+      </c>
+      <c r="G38">
         <v>22317192</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>22766829</v>
       </c>
     </row>
@@ -2659,9 +3024,15 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>313969179</v>
+      </c>
+      <c r="C40">
         <v>37515609</v>
       </c>
-      <c r="E40">
+      <c r="F40">
+        <v>-10271233</v>
+      </c>
+      <c r="G40">
         <v>13967843</v>
       </c>
     </row>
@@ -2675,15 +3046,24 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>313969179</v>
+      </c>
+      <c r="C42">
         <v>37515609</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-37274891</v>
       </c>
       <c r="E42">
+        <v>-23403221</v>
+      </c>
+      <c r="F42">
+        <v>-10271233</v>
+      </c>
+      <c r="G42">
         <v>13967843</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>18468119</v>
       </c>
     </row>
@@ -2692,15 +3072,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>331886653</v>
+      </c>
+      <c r="C43">
         <v>-40830850</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-8283742</v>
       </c>
       <c r="E43">
+        <v>50216263</v>
+      </c>
+      <c r="F43">
+        <v>112040140</v>
+      </c>
+      <c r="G43">
         <v>36285035</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>40152678</v>
       </c>
     </row>
@@ -2715,15 +3104,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>331886653</v>
+      </c>
+      <c r="C46">
         <v>-40830850</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>11422869</v>
       </c>
       <c r="E46">
+        <v>30509652</v>
+      </c>
+      <c r="F46">
+        <v>112040140</v>
+      </c>
+      <c r="G46">
         <v>36285035</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>41234948</v>
       </c>
     </row>
@@ -2734,7 +3132,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2743,15 +3147,24 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>331886653</v>
+      </c>
+      <c r="C48">
         <v>-40830850</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>11422869</v>
       </c>
       <c r="E48">
+        <v>30509652</v>
+      </c>
+      <c r="F48">
+        <v>112040140</v>
+      </c>
+      <c r="G48">
         <v>36285035</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>41234948</v>
       </c>
     </row>
@@ -2761,28 +3174,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>44491534</v>
+      </c>
+      <c r="C50">
         <v>42110846</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>43816390</v>
       </c>
       <c r="E50">
+        <v>40723243</v>
+      </c>
+      <c r="F50">
+        <v>36505994</v>
+      </c>
+      <c r="G50">
         <v>34497793</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>157667909</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2793,6 +3215,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2800,27 +3224,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2834,21 +3264,24 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>433239437</v>
+        <v>415312596</v>
       </c>
       <c r="C3">
+        <v>416243235</v>
+      </c>
+      <c r="D3">
         <v>448686813</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>426559658</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>345482207</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>287515179</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>178947454</v>
       </c>
     </row>
@@ -2872,21 +3305,24 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-370765150</v>
+      </c>
+      <c r="C7">
         <v>-340364029</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-323651484</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-354145398</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-257480356</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-188330683</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-81596607</v>
       </c>
     </row>
@@ -2895,21 +3331,24 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>92875408</v>
+        <v>44547446</v>
       </c>
       <c r="C8">
+        <v>75879206</v>
+      </c>
+      <c r="D8">
         <v>125035329</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>72414260</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>88001851</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>99184496</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>97350847</v>
       </c>
     </row>
@@ -2938,21 +3377,24 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>92875408</v>
+        <v>44547446</v>
       </c>
       <c r="C13">
+        <v>75879206</v>
+      </c>
+      <c r="D13">
         <v>125035329</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>72414260</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>88001851</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>99184496</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>97350847</v>
       </c>
     </row>
@@ -2962,21 +3404,24 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-39019610</v>
+        <v>-23536666</v>
       </c>
       <c r="C15">
+        <v>-30101978</v>
+      </c>
+      <c r="D15">
         <v>-18658866</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-30968678</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-25065759</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-15872106</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-10691285</v>
       </c>
     </row>
@@ -2995,21 +3440,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>-14212004</v>
+        <v>1346031</v>
       </c>
       <c r="C18">
+        <v>2784198</v>
+      </c>
+      <c r="D18">
         <v>2679624</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>1042705</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>2622648</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>6058934</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>10801617</v>
       </c>
     </row>
@@ -3018,21 +3466,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-19865522</v>
+      </c>
+      <c r="C19">
         <v>-17999048</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-15373582</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-10875496</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>-2840412</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>-878099</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-4621841</v>
       </c>
     </row>
@@ -3046,21 +3497,24 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-6678372</v>
+      </c>
+      <c r="C21">
         <v>21644746</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>93682505</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>31612791</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>62718328</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>88493225</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>92839338</v>
       </c>
     </row>
@@ -3079,10 +3533,10 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>1281157</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>6272173</v>
       </c>
     </row>
@@ -3090,7 +3544,7 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>-19680306</v>
       </c>
     </row>
@@ -3129,21 +3583,24 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>68935127</v>
+      </c>
+      <c r="C33">
         <v>47292255</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>93682505</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>31612791</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>62718328</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>70094076</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>99111511</v>
       </c>
     </row>
@@ -3153,21 +3610,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>107929827</v>
+      </c>
+      <c r="C35">
         <v>177606052</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>226241670</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>252903775</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>129246505</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>213370889</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>161654973</v>
       </c>
     </row>
@@ -3176,21 +3636,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-134756458</v>
+      </c>
+      <c r="C36">
         <v>-78353251</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-72684977</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-63208299</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-87348593</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-245531920</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-191427919</v>
       </c>
     </row>
@@ -3204,21 +3667,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>42181648</v>
+      </c>
+      <c r="C38">
         <v>146575547</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>247239198</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>221308267</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>104616240</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>37933045</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>69338565</v>
       </c>
     </row>
@@ -3228,18 +3694,21 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>290806676</v>
+      </c>
+      <c r="C40">
         <v>-33433736</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-56981502</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>17385849</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>14976707</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>358113</v>
       </c>
     </row>
@@ -3247,7 +3716,7 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>-33</v>
       </c>
     </row>
@@ -3256,21 +3725,24 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>290806676</v>
+      </c>
+      <c r="C42">
         <v>-33433736</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-56981502</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>-1238492</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>17385849</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>14976707</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>358080</v>
       </c>
     </row>
@@ -3279,21 +3751,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>332988324</v>
+      </c>
+      <c r="C43">
         <v>113141811</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>190257696</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>238694116</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>122002089</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>52909752</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>69696678</v>
       </c>
     </row>
@@ -3308,21 +3783,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>332988324</v>
+      </c>
+      <c r="C46">
         <v>113141811</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>190257696</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>220069775</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>122002089</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>52909752</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>69696678</v>
       </c>
     </row>
@@ -3336,27 +3814,33 @@
       <c r="C47">
         <v>0</v>
       </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>332988324</v>
+      </c>
+      <c r="C48">
         <v>113141811</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>190257696</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>220069775</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>122002089</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>52909752</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>69696678</v>
       </c>
     </row>
@@ -3366,34 +3850,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>171142013</v>
+      </c>
+      <c r="C50">
         <v>163156473</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>155543420</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>269394939</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>237253862</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>84819402</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>55472384</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3404,6 +3891,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3411,27 +3900,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3445,27 +3940,33 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>46492642</v>
+      </c>
+      <c r="C3">
         <v>13074643</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>286120396</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>202341570</v>
       </c>
-      <c r="E3">
+      <c r="F3">
+        <v>100544410</v>
+      </c>
+      <c r="G3">
         <v>49767187</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>376692638</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>-249981083</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>186927659</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>144911674</v>
       </c>
     </row>
@@ -3474,27 +3975,33 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>291055803</v>
+      </c>
+      <c r="C4">
         <v>-40830850</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>190257696</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>178834827</v>
       </c>
-      <c r="E4">
+      <c r="F4">
+        <v>148325175</v>
+      </c>
+      <c r="G4">
         <v>36285035</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>122002089</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>80767141</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>52909752</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>69696677</v>
       </c>
     </row>
@@ -3503,27 +4010,33 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-164449930</v>
+      </c>
+      <c r="C5">
         <v>47191923</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>127844046</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>54600893</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>23628150</v>
+      </c>
+      <c r="G5">
         <v>46876595</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>250373687</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>-331228190</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>136533277</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>70647067</v>
       </c>
     </row>
@@ -3532,27 +4045,33 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>86602380</v>
+      </c>
+      <c r="C6">
         <v>42110846</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>155543420</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>111727030</v>
       </c>
-      <c r="E6">
+      <c r="F6">
+        <v>71003787</v>
+      </c>
+      <c r="G6">
         <v>34497793</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>237253862</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>79585953</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>84819402</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>55472384</v>
       </c>
     </row>
@@ -3560,7 +4079,7 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0</v>
       </c>
     </row>
@@ -3569,27 +4088,33 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>435109</v>
+      </c>
+      <c r="C8">
         <v>180292</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1997373</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2132705</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>1051523</v>
+      </c>
+      <c r="G8">
         <v>756813</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1085016</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>614232</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>302668</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>121363</v>
       </c>
     </row>
@@ -3613,27 +4138,33 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>27934041</v>
+      </c>
+      <c r="C12">
         <v>16113066</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>132536873</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-36891541</v>
       </c>
-      <c r="E12">
+      <c r="F12">
+        <v>24411926</v>
+      </c>
+      <c r="G12">
         <v>24944632</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-5272151</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>38586220</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-2054919</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-1530385</v>
       </c>
     </row>
@@ -3651,22 +4182,22 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-350298446</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-45209700</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-53370186</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-44882094</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-3495728</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-40750112</v>
       </c>
     </row>
@@ -3695,27 +4226,33 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-351484788</v>
+      </c>
+      <c r="C20">
         <v>-37515609</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>188064826</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>19706611</v>
       </c>
-      <c r="E20">
+      <c r="F20">
+        <v>-3696610</v>
+      </c>
+      <c r="G20">
         <v>-13967843</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>-17385849</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>75989939</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>-14976707</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-358113</v>
       </c>
     </row>
@@ -3728,7 +4265,7 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>-635973</v>
       </c>
     </row>
@@ -3762,27 +4299,33 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-80113231</v>
+      </c>
+      <c r="C28">
         <v>6713570</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-31981346</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-31094150</v>
       </c>
-      <c r="E28">
+      <c r="F28">
+        <v>-71408915</v>
+      </c>
+      <c r="G28">
         <v>-33394443</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>4316862</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>479966</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>-2515370</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>4567930</v>
       </c>
     </row>
@@ -3790,7 +4333,7 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-580444</v>
       </c>
     </row>
@@ -3804,27 +4347,33 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-17347696</v>
+      </c>
+      <c r="C31">
         <v>10857033</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-17667689</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-48888164</v>
       </c>
-      <c r="E31">
+      <c r="F31">
+        <v>-57550348</v>
+      </c>
+      <c r="G31">
         <v>-25816082</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>5792801</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>-36438279</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>-3795052</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-1991389</v>
       </c>
     </row>
@@ -3838,27 +4387,33 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-70445051</v>
+      </c>
+      <c r="C33">
         <v>-33579</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>558666</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>1188309</v>
       </c>
-      <c r="E33">
+      <c r="F33">
+        <v>-3308538</v>
+      </c>
+      <c r="G33">
         <v>1275854</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>8017380</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-175809</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>7520321</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>6327903</v>
       </c>
     </row>
@@ -3892,27 +4447,33 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-1612699</v>
+      </c>
+      <c r="C39">
         <v>-78356</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-149247</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-413230</v>
       </c>
-      <c r="E39">
+      <c r="F39">
+        <v>-191085</v>
+      </c>
+      <c r="G39">
         <v>762184</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>173131</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-549286</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-391821</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-2059531</v>
       </c>
     </row>
@@ -3921,27 +4482,33 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>17476212</v>
+      </c>
+      <c r="C40">
         <v>-159478</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>3044747</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>19286877</v>
       </c>
-      <c r="E40">
+      <c r="F40">
+        <v>14979873</v>
+      </c>
+      <c r="G40">
         <v>-587350</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>11078107</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>20489809</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>2178340</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>-8448033</v>
       </c>
     </row>
@@ -3949,10 +4516,10 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>-8197</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>-88491</v>
       </c>
     </row>
@@ -3961,27 +4528,33 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>1683476</v>
+      </c>
+      <c r="C42">
         <v>1924257</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>245931</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>1172342</v>
       </c>
-      <c r="E42">
+      <c r="F42">
+        <v>1516756</v>
+      </c>
+      <c r="G42">
         <v>584100</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>658208</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>6117882</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>829207</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>-476087</v>
       </c>
     </row>
@@ -3995,27 +4568,33 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-9859663</v>
+      </c>
+      <c r="C44">
         <v>-5787820</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-17433310</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-3703251</v>
       </c>
-      <c r="E44">
+      <c r="F44">
+        <v>-6238170</v>
+      </c>
+      <c r="G44">
         <v>-5207717</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>-498360</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>10830746</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>27661255</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>1887</v>
       </c>
     </row>
@@ -4033,10 +4612,10 @@
       <c r="A47" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>-184625</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>-285236</v>
       </c>
     </row>
@@ -4045,27 +4624,33 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-7810</v>
+      </c>
+      <c r="C48">
         <v>-290</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>0</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-243235</v>
       </c>
-      <c r="E48">
+      <c r="F48">
+        <v>-20617403</v>
+      </c>
+      <c r="G48">
         <v>-4316941</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-6234658</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>154903</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>-874625</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>1042626</v>
       </c>
     </row>
@@ -4074,12 +4659,18 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>46492642</v>
+      </c>
+      <c r="C49">
         <v>13074643</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>286120396</v>
       </c>
-      <c r="E49">
+      <c r="F49">
+        <v>100544410</v>
+      </c>
+      <c r="G49">
         <v>49767187</v>
       </c>
     </row>
@@ -4169,27 +4760,33 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-488773791</v>
+      </c>
+      <c r="C67">
         <v>-533599839</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-49204258</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-43685954</v>
       </c>
-      <c r="E67">
+      <c r="F67">
+        <v>-29777000</v>
+      </c>
+      <c r="G67">
         <v>-16659266</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-4865360</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>-1665315</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>109763</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>-163903</v>
       </c>
     </row>
@@ -4238,6 +4835,9 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
+        <v>-480158053</v>
+      </c>
+      <c r="C76">
         <v>-533378718</v>
       </c>
     </row>
@@ -4251,27 +4851,33 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-8615738</v>
+      </c>
+      <c r="C78">
         <v>-221121</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-49204258</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-43685954</v>
       </c>
-      <c r="E78">
+      <c r="F78">
+        <v>-29777000</v>
+      </c>
+      <c r="G78">
         <v>-16659266</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-157564738</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>-1665315</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>-5872001</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>-5972118</v>
       </c>
     </row>
@@ -4386,27 +4992,33 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>431456800</v>
+      </c>
+      <c r="C101">
         <v>500126481</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>-164631344</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>-91153849</v>
       </c>
-      <c r="E101">
+      <c r="F101">
+        <v>-78430968</v>
+      </c>
+      <c r="G101">
         <v>-22715601</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>-230184273</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>47207479</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>-168788616</v>
       </c>
-      <c r="I101">
+      <c r="K101">
         <v>-140483941</v>
       </c>
     </row>
@@ -4428,6 +5040,9 @@
         <v>544447675</v>
       </c>
       <c r="C104">
+        <v>544447675</v>
+      </c>
+      <c r="D104">
         <v>0</v>
       </c>
     </row>
@@ -4445,10 +5060,10 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="G107">
+      <c r="I107">
         <v>88525000</v>
       </c>
-      <c r="H107">
+      <c r="J107">
         <v>18816970</v>
       </c>
     </row>
@@ -4465,18 +5080,24 @@
         <v>50000000</v>
       </c>
       <c r="C109">
+        <v>50000000</v>
+      </c>
+      <c r="D109">
         <v>125000000</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>60000000</v>
       </c>
-      <c r="E109">
+      <c r="F109">
         <v>50000000</v>
       </c>
-      <c r="F109">
+      <c r="G109">
+        <v>50000000</v>
+      </c>
+      <c r="H109">
         <v>10000000</v>
       </c>
-      <c r="G109">
+      <c r="I109">
         <v>6951196</v>
       </c>
     </row>
@@ -4485,27 +5106,33 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-136861348</v>
+      </c>
+      <c r="C110">
         <v>-77526539</v>
       </c>
-      <c r="C110">
+      <c r="D110">
         <v>-237870260</v>
       </c>
-      <c r="D110">
+      <c r="E110">
         <v>-184909602</v>
       </c>
-      <c r="E110">
+      <c r="F110">
+        <v>-124093140</v>
+      </c>
+      <c r="G110">
         <v>-53450798</v>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>-198202238</v>
       </c>
-      <c r="G110">
+      <c r="I110">
         <v>-86854937</v>
       </c>
-      <c r="H110">
+      <c r="J110">
         <v>-144449911</v>
       </c>
-      <c r="I110">
+      <c r="K110">
         <v>-99622084</v>
       </c>
     </row>
@@ -4524,12 +5151,18 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
+        <v>-463778</v>
+      </c>
+      <c r="C113">
         <v>-2293451</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>-3247231</v>
       </c>
-      <c r="E113">
+      <c r="F113">
+        <v>18949552</v>
+      </c>
+      <c r="G113">
         <v>3648569</v>
       </c>
     </row>
@@ -4558,27 +5191,33 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-26206875</v>
+      </c>
+      <c r="C118">
         <v>-15042330</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-50405861</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>35323647</v>
       </c>
-      <c r="E118">
+      <c r="F118">
+        <v>-24395282</v>
+      </c>
+      <c r="G118">
         <v>-23156366</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-52512446</v>
       </c>
-      <c r="G118">
+      <c r="I118">
         <v>42698578</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>-56322474</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>-42972564</v>
       </c>
     </row>
@@ -4590,24 +5229,30 @@
         <v>541126</v>
       </c>
       <c r="C119">
+        <v>541126</v>
+      </c>
+      <c r="D119">
         <v>1892008</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>-1567894</v>
       </c>
-      <c r="E119">
+      <c r="F119">
+        <v>1107902</v>
+      </c>
+      <c r="G119">
         <v>242994</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>5074031</v>
       </c>
-      <c r="G119">
+      <c r="I119">
         <v>-4112358</v>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>1686799</v>
       </c>
-      <c r="I119">
+      <c r="K119">
         <v>965385</v>
       </c>
     </row>
@@ -4641,12 +5286,18 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-10824349</v>
+      </c>
+      <c r="C125">
         <v>-20398715</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>72284794</v>
       </c>
-      <c r="E125">
+      <c r="F125">
+        <v>-7663558</v>
+      </c>
+      <c r="G125">
         <v>10392320</v>
       </c>
     </row>
@@ -4655,18 +5306,24 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>-4641420</v>
+      </c>
+      <c r="C126">
         <v>-1690097</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>-14752202</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>67501767</v>
       </c>
-      <c r="E126">
+      <c r="F126">
+        <v>-403940</v>
+      </c>
+      <c r="G126">
         <v>-1425070</v>
       </c>
-      <c r="G126">
+      <c r="I126">
         <v>-204438919</v>
       </c>
     </row>
@@ -4675,27 +5332,33 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-15465769</v>
+      </c>
+      <c r="C127">
         <v>-22088812</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>57532592</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>-2623940</v>
       </c>
-      <c r="E127">
+      <c r="F127">
+        <v>-8067498</v>
+      </c>
+      <c r="G127">
         <v>8967250</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>-11056373</v>
       </c>
-      <c r="G127">
+      <c r="I127">
         <v>-2137714</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>12267042</v>
       </c>
-      <c r="I127">
+      <c r="K127">
         <v>-1544385</v>
       </c>
     </row>
@@ -4707,9 +5370,15 @@
         <v>68795052</v>
       </c>
       <c r="C128">
+        <v>68795052</v>
+      </c>
+      <c r="D128">
         <v>11262460</v>
       </c>
-      <c r="E128">
+      <c r="F128">
+        <v>11262460</v>
+      </c>
+      <c r="G128">
         <v>11262460</v>
       </c>
     </row>
@@ -4718,25 +5387,31 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>53329283</v>
+      </c>
+      <c r="C129">
         <v>46706240</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>68795052</v>
       </c>
-      <c r="E129">
+      <c r="F129">
+        <v>3194962</v>
+      </c>
+      <c r="G129">
         <v>20229710</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4747,6 +5422,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4754,27 +5431,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -4788,15 +5471,24 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>33417999</v>
+      </c>
+      <c r="C3">
         <v>13074643</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>83778826</v>
       </c>
       <c r="E3">
+        <v>101797160</v>
+      </c>
+      <c r="F3">
+        <v>50777223</v>
+      </c>
+      <c r="G3">
         <v>49767187</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>626673721</v>
       </c>
     </row>
@@ -4805,15 +5497,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>331886653</v>
+      </c>
+      <c r="C4">
         <v>-40830850</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>11422869</v>
       </c>
       <c r="E4">
+        <v>30509652</v>
+      </c>
+      <c r="F4">
+        <v>112040140</v>
+      </c>
+      <c r="G4">
         <v>36285035</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>41234948</v>
       </c>
     </row>
@@ -4822,15 +5523,24 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-211641853</v>
+      </c>
+      <c r="C5">
         <v>47191923</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>73243153</v>
       </c>
       <c r="E5">
+        <v>30972743</v>
+      </c>
+      <c r="F5">
+        <v>-23248445</v>
+      </c>
+      <c r="G5">
         <v>46876595</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>581601877</v>
       </c>
     </row>
@@ -4839,15 +5549,24 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>44491534</v>
+      </c>
+      <c r="C6">
         <v>42110846</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>43816390</v>
       </c>
       <c r="E6">
+        <v>40723243</v>
+      </c>
+      <c r="F6">
+        <v>36505994</v>
+      </c>
+      <c r="G6">
         <v>34497793</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>157667909</v>
       </c>
     </row>
@@ -4861,15 +5580,24 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>254817</v>
+      </c>
+      <c r="C8">
         <v>180292</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-135332</v>
       </c>
       <c r="E8">
+        <v>1081182</v>
+      </c>
+      <c r="F8">
+        <v>294710</v>
+      </c>
+      <c r="G8">
         <v>756813</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>470784</v>
       </c>
     </row>
@@ -4893,15 +5621,24 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>11820975</v>
+      </c>
+      <c r="C12">
         <v>16113066</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>169428414</v>
       </c>
       <c r="E12">
+        <v>-61303467</v>
+      </c>
+      <c r="F12">
+        <v>-532706</v>
+      </c>
+      <c r="G12">
         <v>24944632</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-43858371</v>
       </c>
     </row>
@@ -4919,10 +5656,10 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-305088746</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-8488092</v>
       </c>
     </row>
@@ -4951,15 +5688,24 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-313969179</v>
+      </c>
+      <c r="C20">
         <v>-37515609</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>168358215</v>
       </c>
       <c r="E20">
+        <v>23403221</v>
+      </c>
+      <c r="F20">
+        <v>10271233</v>
+      </c>
+      <c r="G20">
         <v>-13967843</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>-93375788</v>
       </c>
     </row>
@@ -5003,15 +5749,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-86826801</v>
+      </c>
+      <c r="C28">
         <v>6713570</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-887196</v>
       </c>
       <c r="E28">
+        <v>40314765</v>
+      </c>
+      <c r="F28">
+        <v>-38014472</v>
+      </c>
+      <c r="G28">
         <v>-33394443</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>3836896</v>
       </c>
     </row>
@@ -5030,15 +5785,24 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-28204729</v>
+      </c>
+      <c r="C31">
         <v>10857033</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>31220475</v>
       </c>
       <c r="E31">
+        <v>8662184</v>
+      </c>
+      <c r="F31">
+        <v>-31734266</v>
+      </c>
+      <c r="G31">
         <v>-25816082</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>42231080</v>
       </c>
     </row>
@@ -5052,15 +5816,24 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-70411472</v>
+      </c>
+      <c r="C33">
         <v>-33579</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-629643</v>
       </c>
       <c r="E33">
+        <v>4496847</v>
+      </c>
+      <c r="F33">
+        <v>-4584392</v>
+      </c>
+      <c r="G33">
         <v>1275854</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>8193189</v>
       </c>
     </row>
@@ -5094,15 +5867,24 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-1534343</v>
+      </c>
+      <c r="C39">
         <v>-78356</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>263983</v>
       </c>
       <c r="E39">
+        <v>-222145</v>
+      </c>
+      <c r="F39">
+        <v>-953269</v>
+      </c>
+      <c r="G39">
         <v>762184</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>722417</v>
       </c>
     </row>
@@ -5111,15 +5893,24 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>17635690</v>
+      </c>
+      <c r="C40">
         <v>-159478</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-16242130</v>
       </c>
       <c r="E40">
+        <v>4307004</v>
+      </c>
+      <c r="F40">
+        <v>15567223</v>
+      </c>
+      <c r="G40">
         <v>-587350</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>-9411702</v>
       </c>
     </row>
@@ -5127,10 +5918,10 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>-8197</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>-88491</v>
       </c>
     </row>
@@ -5139,15 +5930,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>-240781</v>
+      </c>
+      <c r="C42">
         <v>1924257</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-926411</v>
       </c>
       <c r="E42">
+        <v>-344414</v>
+      </c>
+      <c r="F42">
+        <v>932656</v>
+      </c>
+      <c r="G42">
         <v>584100</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>-5459674</v>
       </c>
     </row>
@@ -5161,15 +5961,24 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-4071843</v>
+      </c>
+      <c r="C44">
         <v>-5787820</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-13730059</v>
       </c>
       <c r="E44">
+        <v>2534919</v>
+      </c>
+      <c r="F44">
+        <v>-1030453</v>
+      </c>
+      <c r="G44">
         <v>-5207717</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>-11329106</v>
       </c>
     </row>
@@ -5193,15 +6002,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-7520</v>
+      </c>
+      <c r="C48">
         <v>-290</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>243235</v>
       </c>
       <c r="E48">
+        <v>20374168</v>
+      </c>
+      <c r="F48">
+        <v>-16300462</v>
+      </c>
+      <c r="G48">
         <v>-4316941</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-6389561</v>
       </c>
     </row>
@@ -5210,9 +6028,15 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>33417999</v>
+      </c>
+      <c r="C49">
         <v>13074643</v>
       </c>
-      <c r="E49">
+      <c r="F49">
+        <v>50777223</v>
+      </c>
+      <c r="G49">
         <v>49767187</v>
       </c>
     </row>
@@ -5302,15 +6126,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>44826048</v>
+      </c>
+      <c r="C67">
         <v>-533599839</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-5518304</v>
       </c>
       <c r="E67">
+        <v>-13908954</v>
+      </c>
+      <c r="F67">
+        <v>-13117734</v>
+      </c>
+      <c r="G67">
         <v>-16659266</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-3200045</v>
       </c>
     </row>
@@ -5359,6 +6192,9 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
+        <v>53220665</v>
+      </c>
+      <c r="C76">
         <v>-533378718</v>
       </c>
     </row>
@@ -5372,15 +6208,24 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-8394617</v>
+      </c>
+      <c r="C78">
         <v>-221121</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-5518304</v>
       </c>
       <c r="E78">
+        <v>-13908954</v>
+      </c>
+      <c r="F78">
+        <v>-13117734</v>
+      </c>
+      <c r="G78">
         <v>-16659266</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-155899423</v>
       </c>
     </row>
@@ -5495,15 +6340,24 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>-68669681</v>
+      </c>
+      <c r="C101">
         <v>500126481</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>-73477495</v>
       </c>
       <c r="E101">
+        <v>-12722881</v>
+      </c>
+      <c r="F101">
+        <v>-55715367</v>
+      </c>
+      <c r="G101">
         <v>-22715601</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>-277391752</v>
       </c>
     </row>
@@ -5522,6 +6376,9 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
         <v>544447675</v>
       </c>
     </row>
@@ -5550,15 +6407,24 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
         <v>50000000</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>65000000</v>
       </c>
       <c r="E109">
+        <v>10000000</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
         <v>50000000</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>3048804</v>
       </c>
     </row>
@@ -5567,15 +6433,24 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-59334809</v>
+      </c>
+      <c r="C110">
         <v>-77526539</v>
       </c>
-      <c r="C110">
+      <c r="D110">
         <v>-52960658</v>
       </c>
       <c r="E110">
+        <v>-60816462</v>
+      </c>
+      <c r="F110">
+        <v>-70642342</v>
+      </c>
+      <c r="G110">
         <v>-53450798</v>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>-111347301</v>
       </c>
     </row>
@@ -5594,9 +6469,15 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
+        <v>1829673</v>
+      </c>
+      <c r="C113">
         <v>-2293451</v>
       </c>
-      <c r="E113">
+      <c r="F113">
+        <v>15300983</v>
+      </c>
+      <c r="G113">
         <v>3648569</v>
       </c>
     </row>
@@ -5625,15 +6506,24 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-11164545</v>
+      </c>
+      <c r="C118">
         <v>-15042330</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-85729508</v>
       </c>
       <c r="E118">
+        <v>59718929</v>
+      </c>
+      <c r="F118">
+        <v>-1238916</v>
+      </c>
+      <c r="G118">
         <v>-23156366</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-95211024</v>
       </c>
     </row>
@@ -5642,15 +6532,24 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
         <v>541126</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>3459902</v>
       </c>
       <c r="E119">
+        <v>-2675796</v>
+      </c>
+      <c r="F119">
+        <v>864908</v>
+      </c>
+      <c r="G119">
         <v>242994</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>9186389</v>
       </c>
     </row>
@@ -5684,9 +6583,15 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>9574366</v>
+      </c>
+      <c r="C125">
         <v>-20398715</v>
       </c>
-      <c r="E125">
+      <c r="F125">
+        <v>-18055878</v>
+      </c>
+      <c r="G125">
         <v>10392320</v>
       </c>
     </row>
@@ -5695,12 +6600,21 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>-2951323</v>
+      </c>
+      <c r="C126">
         <v>-1690097</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>-82253969</v>
       </c>
       <c r="E126">
+        <v>67905707</v>
+      </c>
+      <c r="F126">
+        <v>1021130</v>
+      </c>
+      <c r="G126">
         <v>-1425070</v>
       </c>
     </row>
@@ -5709,15 +6623,24 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>6623043</v>
+      </c>
+      <c r="C127">
         <v>-22088812</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>60156532</v>
       </c>
       <c r="E127">
+        <v>5443558</v>
+      </c>
+      <c r="F127">
+        <v>-17034748</v>
+      </c>
+      <c r="G127">
         <v>8967250</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>-8918659</v>
       </c>
     </row>
@@ -5726,9 +6649,15 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
         <v>68795052</v>
       </c>
-      <c r="E128">
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
         <v>11262460</v>
       </c>
     </row>
@@ -5737,22 +6666,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>6623043</v>
+      </c>
+      <c r="C129">
         <v>46706240</v>
       </c>
-      <c r="E129">
+      <c r="F129">
+        <v>-17034748</v>
+      </c>
+      <c r="G129">
         <v>20229710</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5763,6 +6698,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5770,27 +6707,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5804,21 +6747,24 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>232068628</v>
+      </c>
+      <c r="C3">
         <v>249427852</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>286120396</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>829015291</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>376692638</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>186927659</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>144911674</v>
       </c>
     </row>
@@ -5827,21 +6773,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>332988324</v>
+      </c>
+      <c r="C4">
         <v>113141811</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>190257696</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>220069775</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>122002089</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>52909752</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>69696677</v>
       </c>
     </row>
@@ -5850,21 +6799,24 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-60234034</v>
+      </c>
+      <c r="C5">
         <v>128159374</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>127844046</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>636202770</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>250373687</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>136533277</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>70647067</v>
       </c>
     </row>
@@ -5873,21 +6825,24 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>171142013</v>
+      </c>
+      <c r="C6">
         <v>163156473</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>155543420</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>269394939</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>237253862</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>84819402</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>55472384</v>
       </c>
     </row>
@@ -5895,7 +6850,7 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0</v>
       </c>
     </row>
@@ -5904,21 +6859,24 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>1380959</v>
+      </c>
+      <c r="C8">
         <v>1420852</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1997373</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2603489</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1085016</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>302668</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>121363</v>
       </c>
     </row>
@@ -5942,21 +6900,24 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>136058988</v>
+      </c>
+      <c r="C12">
         <v>123705307</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>132536873</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>-80749912</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>-5272151</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-2054919</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-1530385</v>
       </c>
     </row>
@@ -5974,19 +6935,19 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-350298446</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-53697792</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-53370186</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-3495728</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-40750112</v>
       </c>
     </row>
@@ -6015,21 +6976,24 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-159723352</v>
+      </c>
+      <c r="C20">
         <v>164517060</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>188064826</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>-73669177</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>-17385849</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>-14976707</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-358113</v>
       </c>
     </row>
@@ -6042,7 +7006,7 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>-635973</v>
       </c>
     </row>
@@ -6076,21 +7040,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-40685662</v>
+      </c>
+      <c r="C28">
         <v>8126667</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-31981346</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-27257254</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>4316862</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>-2515370</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>4567930</v>
       </c>
     </row>
@@ -6098,7 +7065,7 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-580444</v>
       </c>
     </row>
@@ -6112,21 +7079,24 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>22534963</v>
+      </c>
+      <c r="C31">
         <v>19005426</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-17667689</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-6657084</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>5792801</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>-3795052</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-1991389</v>
       </c>
     </row>
@@ -6140,21 +7110,24 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-66577847</v>
+      </c>
+      <c r="C33">
         <v>-750767</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>558666</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>9381498</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>8017380</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>7520321</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>6327903</v>
       </c>
     </row>
@@ -6188,21 +7161,24 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-1570861</v>
+      </c>
+      <c r="C39">
         <v>-989787</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-149247</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>309187</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>173131</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-391821</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-2059531</v>
       </c>
     </row>
@@ -6211,21 +7187,24 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>5541086</v>
+      </c>
+      <c r="C40">
         <v>3472619</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>3044747</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>9875175</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>11078107</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>2178340</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>-8448033</v>
       </c>
     </row>
@@ -6239,21 +7218,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>412651</v>
+      </c>
+      <c r="C42">
         <v>1586088</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>245931</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>-4287332</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>658208</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>829207</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>-476087</v>
       </c>
     </row>
@@ -6267,21 +7249,24 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-21054803</v>
+      </c>
+      <c r="C44">
         <v>-18013413</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-17433310</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-15032357</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>-498360</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>27661255</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>1887</v>
       </c>
     </row>
@@ -6299,10 +7284,10 @@
       <c r="A47" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>-184625</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>-285236</v>
       </c>
     </row>
@@ -6311,21 +7296,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>20609593</v>
+      </c>
+      <c r="C48">
         <v>4316651</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>0</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-6632796</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-6234658</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>-874625</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>1042626</v>
       </c>
     </row>
@@ -6334,9 +7322,12 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>232068628</v>
+      </c>
+      <c r="C49">
         <v>249427852</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>286120396</v>
       </c>
     </row>
@@ -6426,21 +7417,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-508201049</v>
+      </c>
+      <c r="C67">
         <v>-566144831</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-49204258</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-46885999</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-4865360</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>109763</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>-163903</v>
       </c>
     </row>
@@ -6499,21 +7493,24 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-28042996</v>
+      </c>
+      <c r="C78">
         <v>-32766113</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-49204258</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-199585377</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-157564738</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>-5872001</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>-5972118</v>
       </c>
     </row>
@@ -6628,21 +7625,24 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>345256424</v>
+      </c>
+      <c r="C101">
         <v>358210738</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>-164631344</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>-368545601</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>-230184273</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>-168788616</v>
       </c>
-      <c r="I101">
+      <c r="K101">
         <v>-140483941</v>
       </c>
     </row>
@@ -6660,7 +7660,7 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>0</v>
       </c>
     </row>
@@ -6678,7 +7678,7 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H107">
+      <c r="J107">
         <v>18816970</v>
       </c>
     </row>
@@ -6698,9 +7698,12 @@
         <v>125000000</v>
       </c>
       <c r="D109">
+        <v>125000000</v>
+      </c>
+      <c r="E109">
         <v>63048804</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>10000000</v>
       </c>
     </row>
@@ -6709,21 +7712,24 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-250638468</v>
+      </c>
+      <c r="C110">
         <v>-261946001</v>
       </c>
-      <c r="C110">
+      <c r="D110">
         <v>-237870260</v>
       </c>
-      <c r="D110">
+      <c r="E110">
         <v>-296256903</v>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>-198202238</v>
       </c>
-      <c r="H110">
+      <c r="J110">
         <v>-144449911</v>
       </c>
-      <c r="I110">
+      <c r="K110">
         <v>-99622084</v>
       </c>
     </row>
@@ -6742,9 +7748,12 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
+        <v>-22660561</v>
+      </c>
+      <c r="C113">
         <v>-9189251</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>-3247231</v>
       </c>
     </row>
@@ -6773,21 +7782,24 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-52217454</v>
+      </c>
+      <c r="C118">
         <v>-42291825</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-50405861</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>-59887377</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-52512446</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>-56322474</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>-42972564</v>
       </c>
     </row>
@@ -6796,21 +7808,24 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>1325232</v>
+      </c>
+      <c r="C119">
         <v>2190140</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>1892008</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>7618495</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>5074031</v>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>1686799</v>
       </c>
-      <c r="I119">
+      <c r="K119">
         <v>965385</v>
       </c>
     </row>
@@ -6844,9 +7859,12 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>69124003</v>
+      </c>
+      <c r="C125">
         <v>41493759</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>72284794</v>
       </c>
     </row>
@@ -6855,9 +7873,12 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>-18989682</v>
+      </c>
+      <c r="C126">
         <v>-15017229</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>-14752202</v>
       </c>
     </row>
@@ -6866,21 +7887,24 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>50134321</v>
+      </c>
+      <c r="C127">
         <v>26476530</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>57532592</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>-11542599</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>-11056373</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>12267042</v>
       </c>
-      <c r="I127">
+      <c r="K127">
         <v>-1544385</v>
       </c>
     </row>
@@ -6892,6 +7916,9 @@
         <v>68795052</v>
       </c>
       <c r="C128">
+        <v>68795052</v>
+      </c>
+      <c r="D128">
         <v>11262460</v>
       </c>
     </row>
@@ -6900,15 +7927,18 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>118929373</v>
+      </c>
+      <c r="C129">
         <v>95271582</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>68795052</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>